--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -9,7 +9,7 @@
     <x:sheet name="Объявления" sheetId="1" r:id="rId2"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$O$1</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$P$1</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -42,7 +42,10 @@
     <x:t>До метро, мин</x:t>
   </x:si>
   <x:si>
-    <x:t>Цена, ₽</x:t>
+    <x:t>Первая цена, ₽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Цена сейчас, ₽</x:t>
   </x:si>
   <x:si>
     <x:t>Статус</x:t>
@@ -431,7 +434,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:O1"/>
+  <x:dimension ref="A1:P1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.139196" style="0" customWidth="1"/>
@@ -441,17 +444,17 @@
     <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="7.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="8.996339" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20.996339" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="26.710625" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="20.424911" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="21.853482" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="9" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="8.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="20.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="26.710625" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20.424911" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="21.853482" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="9.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:15" s="1" customFormat="1">
+    <x:row r="1" spans="1:16" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -497,9 +500,12 @@
       <x:c r="O1" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
+      <x:c r="P1" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:O1"/>
+  <x:autoFilter ref="A1:P1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -7,9 +7,11 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Объявления" sheetId="1" r:id="rId2"/>
+    <x:sheet name="История цен" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$P$1</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$U$6</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$6</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -36,6 +38,21 @@
     <x:t>Этаж</x:t>
   </x:si>
   <x:si>
+    <x:t>Этажей в доме</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Год постройки</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Тип дома</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Газоснабжение</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Потолки, м</x:t>
+  </x:si>
+  <x:si>
     <x:t>Метро</x:t>
   </x:si>
   <x:si>
@@ -64,6 +81,123 @@
   </x:si>
   <x:si>
     <x:t>Ссылка</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334110300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, 50,6 м², 4/9 этаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Панельный</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Центральное</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Гражданский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>В профиле</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T15:24:18Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>https://spb.cian.ru/sale/flat/334110300/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334909733</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, 44,6 м², 6/9 этаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Академическая</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://spb.cian.ru/sale/flat/334909733/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>330348790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, 44,3 м², 8/9 этаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Проспект Славы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://spb.cian.ru/sale/flat/330348790/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332861239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, 38,7 м², 10/12 этаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 из 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Комендантский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://spb.cian.ru/sale/flat/332861239/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334653328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, 36,8 м², 9/15 этаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 из 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Парк Победы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://spb.cian.ru/sale/flat/334653328/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Дата наблюдения</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Цена, ₽</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -434,27 +568,31 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:P1"/>
+  <x:dimension ref="A1:U6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="5.139196" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.853482" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="44.996339" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="7.710625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="9.567768" style="0" customWidth="1"/>
-    <x:col min="8" max="9" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="8.996339" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="20.996339" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="26.710625" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="20.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="21.853482" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.139196" style="0" customWidth="1"/>
+    <x:col min="7" max="8" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17.567768" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="24.996339" style="0" customWidth="1"/>
+    <x:col min="13" max="14" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="20.996339" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="26.710625" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="20.424911" style="0" customWidth="1"/>
+    <x:col min="20" max="20" width="21.853482" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="37.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:16" s="1" customFormat="1">
+    <x:row r="1" spans="1:21" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -503,9 +641,452 @@
       <x:c r="P1" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
+      <x:c r="Q1" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="R1" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="S1" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="T1" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="U1" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:21">
+      <x:c r="A2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E2" s="0">
+        <x:v>50.6</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G2" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H2" s="0">
+        <x:v>1970</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="K2" s="0">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M2" s="0">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N2" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="O2" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="P2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:21">
+      <x:c r="A3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E3" s="0">
+        <x:v>44.6</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G3" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M3" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N3" s="0">
+        <x:v>14000000</x:v>
+      </x:c>
+      <x:c r="O3" s="0">
+        <x:v>14000000</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T3" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:21">
+      <x:c r="A4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E4" s="0">
+        <x:v>44.3</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G4" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="M4" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N4" s="0">
+        <x:v>13300000</x:v>
+      </x:c>
+      <x:c r="O4" s="0">
+        <x:v>13300000</x:v>
+      </x:c>
+      <x:c r="P4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:21">
+      <x:c r="A5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E5" s="0">
+        <x:v>38.7</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="G5" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="M5" s="0">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N5" s="0">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="O5" s="0">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T5" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:21">
+      <x:c r="A6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E6" s="0">
+        <x:v>36.8</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G6" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="M6" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="O6" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="P6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S6" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:P1"/>
+  <x:autoFilter ref="A1:U6"/>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E6"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="35.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20.139196" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="37.853482" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5" s="1" customFormat="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D3" s="0">
+        <x:v>14000000</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D4" s="0">
+        <x:v>13300000</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D5" s="0">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D6" s="0">
+        <x:v>13000000</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:autoFilter ref="A1:E6"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -86,13 +86,13 @@
     <x:t>334110300</x:t>
   </x:si>
   <x:si>
-    <x:t>2-комн. квартира, 50,6 м², 4/9 этаж</x:t>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
   </x:si>
   <x:si>
     <x:t>2-комн. квартира</x:t>
   </x:si>
   <x:si>
-    <x:t>Санкт-Петербург, Учительская улица, 19К1</x:t>
+    <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
   </x:si>
   <x:si>
     <x:t>4 из 9</x:t>
@@ -113,19 +113,22 @@
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-14T15:49:54.0443570+00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>https://spb.cian.ru/sale/flat/334110300/</x:t>
+    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
   </x:si>
   <x:si>
     <x:t>334909733</x:t>
   </x:si>
   <x:si>
-    <x:t>2-комн. квартира, 44,6 м², 6/9 этаж</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, Гражданский проспект, 83К1</x:t>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
   </x:si>
   <x:si>
     <x:t>6 из 9</x:t>
@@ -134,16 +137,16 @@
     <x:t>Академическая</x:t>
   </x:si>
   <x:si>
-    <x:t>https://spb.cian.ru/sale/flat/334909733/</x:t>
+    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
   </x:si>
   <x:si>
     <x:t>330348790</x:t>
   </x:si>
   <x:si>
-    <x:t>2-комн. квартира, 44,3 м², 8/9 этаж</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, Бухарестская улица, 86К1</x:t>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
   </x:si>
   <x:si>
     <x:t>8 из 9</x:t>
@@ -152,19 +155,19 @@
     <x:t>Проспект Славы</x:t>
   </x:si>
   <x:si>
-    <x:t>https://spb.cian.ru/sale/flat/330348790/</x:t>
+    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
   </x:si>
   <x:si>
     <x:t>332861239</x:t>
   </x:si>
   <x:si>
-    <x:t>1-комн. квартира, 38,7 м², 10/12 этаж</x:t>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
   </x:si>
   <x:si>
     <x:t>1-комн. квартира</x:t>
   </x:si>
   <x:si>
-    <x:t>Санкт-Петербург, улица Маршала Новикова, 9</x:t>
+    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
   </x:si>
   <x:si>
     <x:t>10 из 12</x:t>
@@ -173,25 +176,28 @@
     <x:t>Комендантский проспект</x:t>
   </x:si>
   <x:si>
-    <x:t>https://spb.cian.ru/sale/flat/332861239/</x:t>
+    <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
   </x:si>
   <x:si>
     <x:t>334653328</x:t>
   </x:si>
   <x:si>
-    <x:t>1-комн. квартира, 36,8 м², 9/15 этаж</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, проспект Космонавтов, 22</x:t>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
   </x:si>
   <x:si>
     <x:t>9 из 15</x:t>
   </x:si>
   <x:si>
+    <x:t>Кирпичный</x:t>
+  </x:si>
+  <x:si>
     <x:t>Парк Победы</x:t>
   </x:si>
   <x:si>
-    <x:t>https://spb.cian.ru/sale/flat/334653328/</x:t>
+    <x:t>https://www.cian.ru/sale/flat/334653328/</x:t>
   </x:si>
   <x:si>
     <x:t>Дата наблюдения</x:t>
@@ -572,9 +578,9 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="35.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="55.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="17.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="44.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="55.710625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="8.139196" style="0" customWidth="1"/>
     <x:col min="7" max="8" width="16.996339" style="0" customWidth="1"/>
@@ -586,10 +592,10 @@
     <x:col min="15" max="15" width="16.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="10.710625" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="20.996339" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="26.710625" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="33.139196" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="20.424911" style="0" customWidth="1"/>
     <x:col min="20" max="20" width="21.853482" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="37.853482" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="38.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:21" s="1" customFormat="1">
@@ -710,48 +716,51 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:21">
       <x:c r="A3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>44.6</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G3" s="0">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="H3" s="0">
+        <x:v>1970</x:v>
+      </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M3" s="0">
         <x:v>11</x:v>
@@ -769,48 +778,51 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T3" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:21">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>44.3</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G4" s="0">
         <x:v>9</x:v>
       </x:c>
+      <x:c r="H4" s="0">
+        <x:v>1967</x:v>
+      </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M4" s="0">
         <x:v>9</x:v>
@@ -828,48 +840,51 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:21">
       <x:c r="A5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>38.7</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G5" s="0">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="H5" s="0">
+        <x:v>1986</x:v>
+      </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M5" s="0">
         <x:v>13</x:v>
@@ -887,48 +902,51 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S5" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T5" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:21">
       <x:c r="A6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>36.8</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G6" s="0">
         <x:v>15</x:v>
       </x:c>
+      <x:c r="H6" s="0">
+        <x:v>1970</x:v>
+      </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="J6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M6" s="0">
         <x:v>7</x:v>
@@ -946,16 +964,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="R6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="S6" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -977,10 +995,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="35.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="55.710625" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="20.139196" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="37.853482" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5" s="1" customFormat="1">
@@ -991,10 +1009,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>20</x:v>
@@ -1014,15 +1032,15 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>30</x:v>
@@ -1031,15 +1049,15 @@
         <x:v>14000000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>30</x:v>
@@ -1048,15 +1066,15 @@
         <x:v>13300000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>30</x:v>
@@ -1065,15 +1083,15 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>30</x:v>
@@ -1082,7 +1100,7 @@
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="История цен" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$U$6</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$X$6</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$6</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
@@ -35,6 +35,12 @@
     <x:t>Площадь, м²</x:t>
   </x:si>
   <x:si>
+    <x:t>Кухня, м²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Балкон/лоджия</x:t>
+  </x:si>
+  <x:si>
     <x:t>Этаж</x:t>
   </x:si>
   <x:si>
@@ -56,7 +62,7 @@
     <x:t>Метро</x:t>
   </x:si>
   <x:si>
-    <x:t>До метро, мин</x:t>
+    <x:t>До метро</x:t>
   </x:si>
   <x:si>
     <x:t>Первая цена, ₽</x:t>
@@ -68,16 +74,19 @@
     <x:t>Статус</x:t>
   </x:si>
   <x:si>
-    <x:t>Впервые замечено</x:t>
+    <x:t>Опубликовано на Циане</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Впервые замечено монитором</x:t>
   </x:si>
   <x:si>
     <x:t>Последний раз замечено</x:t>
   </x:si>
   <x:si>
-    <x:t>Дней наблюдения</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Обновлено на Циан</x:t>
+    <x:t>Дней на Циане</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Обновлено на Циане</x:t>
   </x:si>
   <x:si>
     <x:t>Ссылка</x:t>
@@ -95,6 +104,9 @@
     <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
   </x:si>
   <x:si>
+    <x:t>1 балкон</x:t>
+  </x:si>
+  <x:si>
     <x:t>4 из 9</x:t>
   </x:si>
   <x:si>
@@ -107,13 +119,19 @@
     <x:t>Гражданский проспект</x:t>
   </x:si>
   <x:si>
+    <x:t>18 мин пешком</x:t>
+  </x:si>
+  <x:si>
     <x:t>В профиле</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-12T09:46:25.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-14T15:49:54.0443570+00:00</x:t>
+    <x:t>2026-10-14T16:07:05.7223974+00:00</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -137,6 +155,12 @@
     <x:t>Академическая</x:t>
   </x:si>
   <x:si>
+    <x:t>11 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-13T19:57:38.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
   </x:si>
   <x:si>
@@ -155,6 +179,12 @@
     <x:t>Проспект Славы</x:t>
   </x:si>
   <x:si>
+    <x:t>9 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-12T09:46:33.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
   </x:si>
   <x:si>
@@ -176,6 +206,12 @@
     <x:t>Комендантский проспект</x:t>
   </x:si>
   <x:si>
+    <x:t>13 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-13T19:52:22.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
   </x:si>
   <x:si>
@@ -188,6 +224,9 @@
     <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
   </x:si>
   <x:si>
+    <x:t>1 лоджия</x:t>
+  </x:si>
+  <x:si>
     <x:t>9 из 15</x:t>
   </x:si>
   <x:si>
@@ -195,6 +234,12 @@
   </x:si>
   <x:si>
     <x:t>Парк Победы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7 мин на транспорте</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-12T09:46:40.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334653328/</x:t>
@@ -574,7 +619,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:U6"/>
+  <x:dimension ref="A1:X6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
@@ -582,23 +627,27 @@
     <x:col min="3" max="3" width="17.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="55.710625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="7" max="8" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="17.567768" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.567768" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="24.996339" style="0" customWidth="1"/>
-    <x:col min="13" max="14" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="20.996339" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="33.139196" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="20.424911" style="0" customWidth="1"/>
-    <x:col min="20" max="20" width="21.853482" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="38.996339" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="10" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17.567768" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="24.996339" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="20.282054" style="0" customWidth="1"/>
+    <x:col min="16" max="16" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="17" max="17" width="16.567768" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="20" max="20" width="32.567768" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="33.139196" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="16.996339" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="22.853482" style="0" customWidth="1"/>
+    <x:col min="24" max="24" width="38.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:21" s="1" customFormat="1">
+    <x:row r="1" spans="1:24" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -662,322 +711,382 @@
       <x:c r="U1" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
+      <x:c r="V1" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="W1" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="X1" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:21">
+    <x:row r="2" spans="1:24">
       <x:c r="A2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="0">
         <x:v>50.6</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G2" s="0">
+      <x:c r="F2" s="0">
+        <x:v>5.8</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H2" s="0">
+      <x:c r="J2" s="0">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s">
+      <x:c r="K2" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M2" s="0">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="P2" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="U2" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V2" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="X2" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:24">
+      <x:c r="A3" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="K2" s="0">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="M2" s="0">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="N2" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="O2" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="T2" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="U2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:21">
-      <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>44.6</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="G3" s="0">
+      <x:c r="F3" s="0">
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I3" s="0">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H3" s="0">
+      <x:c r="J3" s="0">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="K3" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="M3" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="N3" s="0">
+      <x:c r="N3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="P3" s="0">
         <x:v>14000000</x:v>
       </x:c>
-      <x:c r="O3" s="0">
+      <x:c r="Q3" s="0">
         <x:v>14000000</x:v>
       </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="R3" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S3" s="0">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="T3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W3" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="X3" s="0" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:21">
+    <x:row r="4" spans="1:24">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>44.3</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="G4" s="0">
+      <x:c r="F4" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I4" s="0">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H4" s="0">
+      <x:c r="J4" s="0">
         <x:v>1967</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="K4" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="M4" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="N4" s="0">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="N4" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="O4" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="P4" s="0">
         <x:v>13300000</x:v>
       </x:c>
-      <x:c r="O4" s="0">
+      <x:c r="Q4" s="0">
         <x:v>13300000</x:v>
       </x:c>
-      <x:c r="P4" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q4" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S4" s="0">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>54</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W4" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="X4" s="0" t="s">
+        <x:v>55</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:21">
+    <x:row r="5" spans="1:24">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>38.7</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G5" s="0">
+      <x:c r="F5" s="0">
+        <x:v>10.1</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I5" s="0">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H5" s="0">
+      <x:c r="J5" s="0">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="J5" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="K5" s="0" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M5" s="0">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="N5" s="0">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="P5" s="0">
         <x:v>12990000</x:v>
       </x:c>
-      <x:c r="O5" s="0">
+      <x:c r="Q5" s="0">
         <x:v>12990000</x:v>
       </x:c>
-      <x:c r="P5" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q5" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S5" s="0">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="T5" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V5" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="X5" s="0" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:21">
+    <x:row r="6" spans="1:24">
       <x:c r="A6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>36.8</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G6" s="0">
+      <x:c r="F6" s="0">
+        <x:v>7.8</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I6" s="0">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H6" s="0">
+      <x:c r="J6" s="0">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J6" s="0" t="s">
-        <x:v>32</x:v>
+      <x:c r="K6" s="0" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="M6" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="N6" s="0">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="P6" s="0">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="O6" s="0">
+      <x:c r="Q6" s="0">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="P6" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="Q6" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="R6" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="S6" s="0">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>73</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V6" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W6" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="X6" s="0" t="s">
+        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:U6"/>
+  <x:autoFilter ref="A1:X6"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -1009,98 +1118,98 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D2" s="0">
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>14000000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D4" s="0">
         <x:v>13300000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -131,7 +131,7 @@
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-14T16:07:05.7223974+00:00</x:t>
+    <x:t>2026-10-14T16:12:16.7719322+00:00</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -832,6 +832,9 @@
       <x:c r="L3" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="M3" s="0">
+        <x:v>2.5</x:v>
+      </x:c>
       <x:c r="N3" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -901,7 +904,10 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M4" s="0">
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>52</x:v>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -11,7 +11,7 @@
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$X$6</x:definedName>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$6</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$7</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -86,7 +86,7 @@
     <x:t>Дней на Циане</x:t>
   </x:si>
   <x:si>
-    <x:t>Обновлено на Циане</x:t>
+    <x:t>Дата addedTimestamp из API (не первая публикация)</x:t>
   </x:si>
   <x:si>
     <x:t>Ссылка</x:t>
@@ -125,30 +125,33 @@
     <x:t>В профиле</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T15:24:18Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T17:11:29.7796317+00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-12T09:46:25.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-14T15:24:18Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T16:12:16.7719322+00:00</x:t>
+    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334909733</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334909733</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
     <x:t>6 из 9</x:t>
   </x:si>
   <x:si>
@@ -158,6 +161,9 @@
     <x:t>11 мин пешком</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-13T19:57:38.0000000+03:00</x:t>
   </x:si>
   <x:si>
@@ -182,7 +188,10 @@
     <x:t>9 мин пешком</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-12T09:46:33.0000000+03:00</x:t>
+    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T19:26:32.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
@@ -209,6 +218,9 @@
     <x:t>13 мин пешком</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-13T19:52:22.0000000+03:00</x:t>
   </x:si>
   <x:si>
@@ -237,6 +249,9 @@
   </x:si>
   <x:si>
     <x:t>7 мин на транспорте</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>2026-10-12T09:46:40.0000000+03:00</x:t>
@@ -643,7 +658,7 @@
     <x:col min="20" max="20" width="32.567768" style="0" customWidth="1"/>
     <x:col min="21" max="21" width="33.139196" style="0" customWidth="1"/>
     <x:col min="22" max="22" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="22.853482" style="0" customWidth="1"/>
+    <x:col min="23" max="23" width="52.710625" style="0" customWidth="1"/>
     <x:col min="24" max="24" width="38.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -786,7 +801,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="V2" s="0">
-        <x:v>3</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="W2" s="0" t="s">
         <x:v>38</x:v>
@@ -815,10 +830,10 @@
         <x:v>7.8</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>9</x:v>
@@ -830,16 +845,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M3" s="0">
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="P3" s="0">
         <x:v>14000000</x:v>
@@ -851,7 +866,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="T3" s="0" t="s">
         <x:v>36</x:v>
@@ -863,24 +878,24 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="X3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:24">
       <x:c r="A4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>44.3</x:v>
@@ -889,10 +904,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>9</x:v>
@@ -910,22 +925,22 @@
         <x:v>2.55</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="P4" s="0">
         <x:v>13300000</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>13300000</x:v>
+        <x:v>13200000</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
         <x:v>36</x:v>
@@ -934,27 +949,27 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>3</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="X4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24">
       <x:c r="A5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>38.7</x:v>
@@ -966,7 +981,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>12</x:v>
@@ -978,16 +993,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M5" s="0">
         <x:v>2.65</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P5" s="0">
         <x:v>12990000</x:v>
@@ -999,7 +1014,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="T5" s="0" t="s">
         <x:v>36</x:v>
@@ -1008,27 +1023,27 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>2</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="X5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:24">
       <x:c r="A6" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>36.8</x:v>
@@ -1037,10 +1052,10 @@
         <x:v>7.8</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>15</x:v>
@@ -1049,19 +1064,19 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M6" s="0">
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="P6" s="0">
         <x:v>13000000</x:v>
@@ -1073,7 +1088,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
         <x:v>36</x:v>
@@ -1082,13 +1097,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>3</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="X6" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1106,12 +1121,12 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E6"/>
+  <x:dimension ref="A1:E7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="55.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="33.139196" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="9.996339" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="38.996339" style="0" customWidth="1"/>
   </x:cols>
@@ -1124,10 +1139,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>23</x:v>
@@ -1164,15 +1179,15 @@
         <x:v>14000000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>36</x:v>
@@ -1181,45 +1196,62 @@
         <x:v>13300000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>12990000</x:v>
+        <x:v>13200000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D6" s="0">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D7" s="0">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>74</x:v>
+      <x:c r="E7" s="0" t="s">
+        <x:v>79</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:E6"/>
+  <x:autoFilter ref="A1:E7"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -1,281 +1,275 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet name="Объявления" sheetId="1" r:id="rId2"/>
-    <x:sheet name="История цен" sheetId="2" r:id="rId3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="Rcadb430f078240e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История цен" sheetId="2" r:id="R6d54ac61e1b147d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Старый архив" sheetId="3" r:id="Ra52960e56ed840c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены старого архива" sheetId="4" r:id="R24dff7f110a84da6"/>
   </x:sheets>
-  <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$X$6</x:definedName>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$7</x:definedName>
-  </x:definedNames>
-  <x:calcPr calcId="125725"/>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Объявление</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Тип</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Адрес</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Площадь, м²</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Кухня, м²</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Балкон/лоджия</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Этаж</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Этажей в доме</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Год постройки</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Тип дома</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Газоснабжение</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Потолки, м</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Метро</x:t>
-  </x:si>
-  <x:si>
-    <x:t>До метро</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Первая цена, ₽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Цена сейчас, ₽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Статус</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Опубликовано на Циане</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Впервые замечено монитором</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Последний раз замечено</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дней на Циане</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата addedTimestamp из API (не первая публикация)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ссылка</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334110300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 балкон</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Панельный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Центральное</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Гражданский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>В профиле</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T15:24:18Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T17:11:29.7796317+00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-12T09:46:25.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334909733</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>6 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Академическая</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-13T19:57:38.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>330348790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Проспект Славы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T19:26:32.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>332861239</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10 из 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Комендантский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-13T19:52:22.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334653328</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 лоджия</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 из 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Кирпичный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Парк Победы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7 мин на транспорте</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-12T09:46:40.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334653328/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата наблюдения</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Цена, ₽</x:t>
+    <x:t xml:space="preserve">ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Объявление</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Тип</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Адрес</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Площадь, м²</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Кухня, м²</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Балкон/лоджия</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Этаж</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Этажей в доме</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Год постройки</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Тип дома</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Газоснабжение</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Потолки, м</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Метро</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">До метро</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Первая цена, ₽</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Цена сейчас, ₽</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Статус</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Опубликовано на Циане</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Впервые замечено монитором</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Последний раз замечено</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Дней на Циане</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Дата addedTimestamp из API (не первая публикация)</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Ссылка</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">334110300</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 балкон</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">4 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Панельный</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Центральное</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Гражданский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">18 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">В профиле</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-09-21T09:12:08.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-14T15:24:18Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-14T17:11:29.7796317+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-12T09:46:25.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.cian.ru/sale/flat/334110300/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">334909733</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">43</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">6 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Академическая</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">11 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-13T19:40:19.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-13T19:57:38.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.cian.ru/sale/flat/334909733/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">330348790</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">8 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Проспект Славы</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">9 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-05-24T11:43:17.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-14T19:26:32.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.cian.ru/sale/flat/330348790/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">332861239</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">10 из 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Комендантский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">13 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-08-12T11:55:30.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-13T19:52:22.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.cian.ru/sale/flat/332861239/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">334653328</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1 лоджия</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">9 из 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Кирпичный</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Парк Победы</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">7 мин на транспорте</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-07T08:38:25.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2026-10-12T09:46:40.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://www.cian.ru/sale/flat/334653328/</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Дата наблюдения</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Цена, ₽</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="0" formatCode=""/>
+    <x:numFmt numFmtId="200" formatCode="dd.mm.yyyy"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="5">
     <x:font>
-      <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
@@ -283,14 +277,33 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF5A3200"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17202A"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF17202A"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -302,24 +315,44 @@
         <x:fgColor rgb="FFEAF1FA"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE6C0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE6C0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFE6C0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
-      </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
-      </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
-      </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
-      </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
+      <x:left style="none"/>
+      <x:right style="none"/>
+      <x:top style="none"/>
+      <x:bottom style="none"/>
+      <x:diagonal style="none"/>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="2">
@@ -330,18 +363,51 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0"/>
       <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
 </file>
@@ -510,7 +576,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -519,13 +585,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -559,17 +625,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -624,45 +679,39 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:X6"/>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="55.710625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="17.996339" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="8.139196" style="0" customWidth="1"/>
-    <x:col min="9" max="10" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11.996339" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="17.567768" style="0" customWidth="1"/>
-    <x:col min="13" max="13" width="13.567768" style="0" customWidth="1"/>
-    <x:col min="14" max="14" width="24.996339" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="20.282054" style="0" customWidth="1"/>
-    <x:col min="16" max="16" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="17" max="17" width="16.567768" style="0" customWidth="1"/>
-    <x:col min="18" max="18" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="33.139196" style="0" customWidth="1"/>
-    <x:col min="20" max="20" width="32.567768" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="33.139196" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="16.996339" style="0" customWidth="1"/>
-    <x:col min="23" max="23" width="52.710625" style="0" customWidth="1"/>
-    <x:col min="24" max="24" width="38.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.28205394744873" customWidth="1"/>
+    <x:col min="2" max="2" width="55.71062469482422" customWidth="1"/>
+    <x:col min="3" max="3" width="17.424911499023438" customWidth="1"/>
+    <x:col min="4" max="4" width="55.71062469482422" customWidth="1"/>
+    <x:col min="5" max="5" width="15.139196395874023" customWidth="1"/>
+    <x:col min="6" max="6" width="11.853482246398926" customWidth="1"/>
+    <x:col min="7" max="7" width="17.996339797973633" customWidth="1"/>
+    <x:col min="8" max="8" width="8.139196395874023" customWidth="1"/>
+    <x:col min="9" max="10" width="16.996339797973633" customWidth="1"/>
+    <x:col min="11" max="11" width="11.996338844299316" customWidth="1"/>
+    <x:col min="12" max="12" width="17.567768096923828" customWidth="1"/>
+    <x:col min="13" max="13" width="13.567768096923828" customWidth="1"/>
+    <x:col min="14" max="14" width="24.996339797973633" customWidth="1"/>
+    <x:col min="15" max="15" width="20.282054901123047" customWidth="1"/>
+    <x:col min="16" max="16" width="16.996339797973633" customWidth="1"/>
+    <x:col min="17" max="17" width="16.567768096923828" customWidth="1"/>
+    <x:col min="18" max="18" width="10.710624694824219" customWidth="1"/>
+    <x:col min="19" max="19" width="33.13919448852539" customWidth="1"/>
+    <x:col min="20" max="20" width="32.56776809692383" customWidth="1"/>
+    <x:col min="21" max="21" width="33.13919448852539" customWidth="1"/>
+    <x:col min="22" max="22" width="16.996339797973633" customWidth="1"/>
+    <x:col min="23" max="23" width="52.71062469482422" customWidth="1"/>
+    <x:col min="24" max="24" width="38.996337890625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:24" s="1" customFormat="1">
+    <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -736,402 +785,393 @@
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:24">
-      <x:c r="A2" s="0" t="s">
+    <x:row r="2">
+      <x:c r="A2" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E2" s="0">
+      <x:c r="E2">
         <x:v>50.6</x:v>
       </x:c>
-      <x:c r="F2" s="0">
+      <x:c r="F2">
         <x:v>5.8</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="G2" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
+      <x:c r="H2" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="I2" s="0">
+      <x:c r="I2">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J2" s="0">
+      <x:c r="J2">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="K2" s="0" t="s">
+      <x:c r="K2" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
+      <x:c r="L2" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="M2" s="0">
+      <x:c r="M2">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="N2" s="0" t="s">
+      <x:c r="N2" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="O2" s="0" t="s">
+      <x:c r="O2" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="P2" s="0">
+      <x:c r="P2">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="Q2" s="0">
+      <x:c r="Q2">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="R2" s="0" t="s">
+      <x:c r="R2" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S2" s="0" t="s">
+      <x:c r="S2" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="T2" s="0" t="s">
+      <x:c r="T2" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="U2" s="0" t="s">
+      <x:c r="U2" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="V2" s="0">
+      <x:c r="V2">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="W2" s="0" t="s">
+      <x:c r="W2" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="X2" s="0" t="s">
+      <x:c r="X2" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:24">
-      <x:c r="A3" s="0" t="s">
+    <x:row r="3">
+      <x:c r="A3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D3" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="E3" s="0">
+      <x:c r="E3">
         <x:v>44.6</x:v>
       </x:c>
-      <x:c r="F3" s="0">
+      <x:c r="F3">
         <x:v>7.8</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="G3" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
+      <x:c r="H3" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="I3" s="0">
+      <x:c r="I3">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J3" s="0">
+      <x:c r="J3">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
+      <x:c r="K3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L3" s="0" t="s">
+      <x:c r="L3" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="M3" s="0">
+      <x:c r="M3">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="N3" s="0" t="s">
+      <x:c r="N3" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="O3" s="0" t="s">
+      <x:c r="O3" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="P3" s="0">
+      <x:c r="P3">
         <x:v>14000000</x:v>
       </x:c>
-      <x:c r="Q3" s="0">
+      <x:c r="Q3">
         <x:v>14000000</x:v>
       </x:c>
-      <x:c r="R3" s="0" t="s">
+      <x:c r="R3" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S3" s="0" t="s">
+      <x:c r="S3" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="T3" s="0" t="s">
+      <x:c r="T3" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="U3" s="0" t="s">
+      <x:c r="U3" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="V3" s="0">
+      <x:c r="V3">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="W3" s="0" t="s">
+      <x:c r="W3" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="X3" s="0" t="s">
+      <x:c r="X3" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:24">
-      <x:c r="A4" s="0" t="s">
+    <x:row r="4">
+      <x:c r="A4" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D4" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="E4" s="0">
+      <x:c r="E4">
         <x:v>44.3</x:v>
       </x:c>
-      <x:c r="F4" s="0">
+      <x:c r="F4">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
+      <x:c r="G4" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="H4" s="0" t="s">
+      <x:c r="H4" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="I4" s="0">
+      <x:c r="I4">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J4" s="0">
+      <x:c r="J4">
         <x:v>1967</x:v>
       </x:c>
-      <x:c r="K4" s="0" t="s">
+      <x:c r="K4" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L4" s="0" t="s">
+      <x:c r="L4" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="M4" s="0">
+      <x:c r="M4">
         <x:v>2.55</x:v>
       </x:c>
-      <x:c r="N4" s="0" t="s">
+      <x:c r="N4" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="O4" s="0" t="s">
+      <x:c r="O4" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="P4" s="0">
+      <x:c r="P4">
         <x:v>13300000</x:v>
       </x:c>
-      <x:c r="Q4" s="0">
+      <x:c r="Q4">
         <x:v>13200000</x:v>
       </x:c>
-      <x:c r="R4" s="0" t="s">
+      <x:c r="R4" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S4" s="0" t="s">
+      <x:c r="S4" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="T4" s="0" t="s">
+      <x:c r="T4" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="U4" s="0" t="s">
+      <x:c r="U4" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="V4" s="0">
+      <x:c r="V4">
         <x:v>144</x:v>
       </x:c>
-      <x:c r="W4" s="0" t="s">
+      <x:c r="W4" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="X4" s="0" t="s">
+      <x:c r="X4" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:24">
-      <x:c r="A5" s="0" t="s">
+    <x:row r="5">
+      <x:c r="A5" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>38.7</x:v>
       </x:c>
-      <x:c r="F5" s="0">
+      <x:c r="F5">
         <x:v>10.1</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="G5" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="H5" s="0" t="s">
+      <x:c r="H5" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="I5" s="0">
+      <x:c r="I5">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J5" s="0">
+      <x:c r="J5">
         <x:v>1986</x:v>
       </x:c>
-      <x:c r="K5" s="0" t="s">
+      <x:c r="K5" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="L5" s="0" t="s">
+      <x:c r="L5" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="M5" s="0">
+      <x:c r="M5">
         <x:v>2.65</x:v>
       </x:c>
-      <x:c r="N5" s="0" t="s">
+      <x:c r="N5" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="O5" s="0" t="s">
+      <x:c r="O5" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="P5" s="0">
+      <x:c r="P5">
         <x:v>12990000</x:v>
       </x:c>
-      <x:c r="Q5" s="0">
+      <x:c r="Q5">
         <x:v>12990000</x:v>
       </x:c>
-      <x:c r="R5" s="0" t="s">
+      <x:c r="R5" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S5" s="0" t="s">
+      <x:c r="S5" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="T5" s="0" t="s">
+      <x:c r="T5" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="U5" s="0" t="s">
+      <x:c r="U5" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="V5" s="0">
+      <x:c r="V5">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="W5" s="0" t="s">
+      <x:c r="W5" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="X5" s="0" t="s">
+      <x:c r="X5" t="s">
         <x:v>68</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:24">
-      <x:c r="A6" s="0" t="s">
+    <x:row r="6">
+      <x:c r="A6" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E6" s="0">
+      <x:c r="E6">
         <x:v>36.8</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F6">
         <x:v>7.8</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="G6" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="H6" s="0" t="s">
+      <x:c r="H6" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="I6" s="0">
+      <x:c r="I6">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J6" s="0">
+      <x:c r="J6">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="K6" s="0" t="s">
+      <x:c r="K6" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="L6" s="0" t="s">
+      <x:c r="L6" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="M6" s="0">
+      <x:c r="M6">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="N6" s="0" t="s">
+      <x:c r="N6" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="O6" s="0" t="s">
+      <x:c r="O6" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="P6" s="0">
+      <x:c r="P6">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="Q6" s="0">
+      <x:c r="Q6">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="R6" s="0" t="s">
+      <x:c r="R6" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S6" s="0" t="s">
+      <x:c r="S6" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="T6" s="0" t="s">
+      <x:c r="T6" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="U6" s="0" t="s">
+      <x:c r="U6" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="V6" s="0">
+      <x:c r="V6">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="W6" s="0" t="s">
+      <x:c r="W6" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="X6" s="0" t="s">
+      <x:c r="X6" t="s">
         <x:v>79</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:X6"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:E7"/>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10.282054" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="33.139196" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38.996339" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10.28205394744873" customWidth="1"/>
+    <x:col min="2" max="2" width="55.71062469482422" customWidth="1"/>
+    <x:col min="3" max="3" width="33.13919448852539" customWidth="1"/>
+    <x:col min="4" max="4" width="9.996338844299316" customWidth="1"/>
+    <x:col min="5" max="5" width="38.996337890625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" s="1" customFormat="1">
+    <x:row r="1" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1148,114 +1188,1982 @@
         <x:v>23</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:5">
-      <x:c r="A2" s="0" t="s">
+    <x:row r="2">
+      <x:c r="A2" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D2" s="0">
+      <x:c r="D2">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="E2" t="s">
         <x:v>39</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:5">
-      <x:c r="A3" s="0" t="s">
+    <x:row r="3">
+      <x:c r="A3" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D3" s="0">
+      <x:c r="D3">
         <x:v>14000000</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="E3" t="s">
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0" t="s">
+    <x:row r="4">
+      <x:c r="A4" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D4" s="0">
+      <x:c r="D4">
         <x:v>13300000</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="E4" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:5">
-      <x:c r="A5" s="0" t="s">
+    <x:row r="5">
+      <x:c r="A5" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>13200000</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="E5" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:5">
-      <x:c r="A6" s="0" t="s">
+    <x:row r="6">
+      <x:c r="A6" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D6" s="0">
+      <x:c r="D6">
         <x:v>12990000</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="E6" t="s">
         <x:v>68</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:5">
-      <x:c r="A7" s="0" t="s">
+    <x:row r="7">
+      <x:c r="A7" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="C7" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D7" s="0">
+      <x:c r="D7">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="s">
+      <x:c r="E7" t="s">
         <x:v>79</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:E7"/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="30" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="11" t="str">
+        <x:v>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — из заметок пользователя, не сверены с Цианом. Исчезновение объявления не подтверждает продажу.</x:v>
+      </x:c>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+      <x:c r="F1" s="11"/>
+      <x:c r="G1" s="11"/>
+      <x:c r="H1" s="11"/>
+      <x:c r="I1" s="11"/>
+      <x:c r="J1" s="11"/>
+      <x:c r="K1" s="11"/>
+      <x:c r="L1" s="11"/>
+      <x:c r="M1" s="11"/>
+      <x:c r="N1" s="11"/>
+      <x:c r="O1" s="11"/>
+      <x:c r="P1" s="11"/>
+      <x:c r="Q1" s="11"/>
+      <x:c r="R1" s="11"/>
+      <x:c r="S1" s="11"/>
+      <x:c r="T1" s="11"/>
+      <x:c r="U1" s="11"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>ID заметки</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>Адрес</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>Тип</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str">
+        <x:v>Площадь, м²</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
+        <x:v>Первая дата в заметках</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Первая цена, ₽</x:v>
+      </x:c>
+      <x:c r="G2" s="12" t="str">
+        <x:v>Последняя цена, ₽</x:v>
+      </x:c>
+      <x:c r="H2" s="12" t="str">
+        <x:v>Статус из заметок</x:v>
+      </x:c>
+      <x:c r="I2" s="12" t="str">
+        <x:v>Дата статуса</x:v>
+      </x:c>
+      <x:c r="J2" s="12" t="str">
+        <x:v>Дней по заметкам</x:v>
+      </x:c>
+      <x:c r="K2" s="12" t="str">
+        <x:v>Этаж</x:v>
+      </x:c>
+      <x:c r="L2" s="12" t="str">
+        <x:v>Тип дома</x:v>
+      </x:c>
+      <x:c r="M2" s="12" t="str">
+        <x:v>Год постройки</x:v>
+      </x:c>
+      <x:c r="N2" s="12" t="str">
+        <x:v>Кухня, м²</x:v>
+      </x:c>
+      <x:c r="O2" s="12" t="str">
+        <x:v>Потолки, м</x:v>
+      </x:c>
+      <x:c r="P2" s="12" t="str">
+        <x:v>Балкон</x:v>
+      </x:c>
+      <x:c r="Q2" s="12" t="str">
+        <x:v>Газ</x:v>
+      </x:c>
+      <x:c r="R2" s="12" t="str">
+        <x:v>Лифт</x:v>
+      </x:c>
+      <x:c r="S2" s="12" t="str">
+        <x:v>Метро / время</x:v>
+      </x:c>
+      <x:c r="T2" s="12" t="str">
+        <x:v>Покупка, ₽</x:v>
+      </x:c>
+      <x:c r="U2" s="12" t="str">
+        <x:v>Ремонт, ₽</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="6" t="str">
+        <x:v>manual-01</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str"/>
+      <x:c r="D3" s="6" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="n">
+        <x:v>46048</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="n">
+        <x:v>9990000</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="n">
+        <x:v>9600000</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>Цена продажи — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="n">
+        <x:v>46119</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str"/>
+      <x:c r="L3" s="6" t="str"/>
+      <x:c r="M3" s="6"/>
+      <x:c r="N3" s="6"/>
+      <x:c r="O3" s="6"/>
+      <x:c r="P3" s="6" t="str"/>
+      <x:c r="Q3" s="6" t="str"/>
+      <x:c r="R3" s="6" t="str"/>
+      <x:c r="S3" s="6" t="str"/>
+      <x:c r="T3" s="8" t="n">
+        <x:v>5950000</x:v>
+      </x:c>
+      <x:c r="U3" s="8" t="n">
+        <x:v>2100000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>manual-02</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str"/>
+      <x:c r="D4" s="6" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="n">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="F4" s="8" t="n">
+        <x:v>11700000</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="n">
+        <x:v>11500000</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>Исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I4" s="7" t="n">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str"/>
+      <x:c r="L4" s="6" t="str"/>
+      <x:c r="M4" s="6"/>
+      <x:c r="N4" s="6"/>
+      <x:c r="O4" s="6"/>
+      <x:c r="P4" s="6" t="str"/>
+      <x:c r="Q4" s="6" t="str"/>
+      <x:c r="R4" s="6" t="str"/>
+      <x:c r="S4" s="6" t="str"/>
+      <x:c r="T4" s="8"/>
+      <x:c r="U4" s="8"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="6" t="str">
+        <x:v>manual-03</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Стародеревенская улица, 6</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str"/>
+      <x:c r="D5" s="6" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="n">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="F5" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="n">
+        <x:v>12500000</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I5" s="7"/>
+      <x:c r="J5" s="6"/>
+      <x:c r="K5" s="6" t="str">
+        <x:v>17 из 17</x:v>
+      </x:c>
+      <x:c r="L5" s="6" t="str">
+        <x:v>Панельный</x:v>
+      </x:c>
+      <x:c r="M5" s="6" t="n">
+        <x:v>1991</x:v>
+      </x:c>
+      <x:c r="N5" s="6"/>
+      <x:c r="O5" s="6"/>
+      <x:c r="P5" s="6" t="str">
+        <x:v>Есть</x:v>
+      </x:c>
+      <x:c r="Q5" s="6" t="str"/>
+      <x:c r="R5" s="6" t="str"/>
+      <x:c r="S5" s="6" t="str">
+        <x:v>Старая Деревня 11–15 мин (способ не указан)</x:v>
+      </x:c>
+      <x:c r="T5" s="8"/>
+      <x:c r="U5" s="8"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str"/>
+      <x:c r="D6" s="6" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E6" s="7" t="n">
+        <x:v>46076</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="n">
+        <x:v>22990000</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="n">
+        <x:v>22000000</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>Продано 25.06 — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I6" s="7" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J6" s="6"/>
+      <x:c r="K6" s="6" t="str"/>
+      <x:c r="L6" s="6" t="str"/>
+      <x:c r="M6" s="6"/>
+      <x:c r="N6" s="6"/>
+      <x:c r="O6" s="6"/>
+      <x:c r="P6" s="6" t="str"/>
+      <x:c r="Q6" s="6" t="str"/>
+      <x:c r="R6" s="6" t="str"/>
+      <x:c r="S6" s="6" t="str">
+        <x:v>Электросила</x:v>
+      </x:c>
+      <x:c r="T6" s="8"/>
+      <x:c r="U6" s="8"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="6" t="str">
+        <x:v>manual-05</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str"/>
+      <x:c r="D7" s="6" t="n">
+        <x:v>37.8</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="n">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="n">
+        <x:v>17400000</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="n">
+        <x:v>16990000</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>Исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I7" s="7" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="J7" s="6"/>
+      <x:c r="K7" s="6" t="str"/>
+      <x:c r="L7" s="6" t="str"/>
+      <x:c r="M7" s="6"/>
+      <x:c r="N7" s="6"/>
+      <x:c r="O7" s="6"/>
+      <x:c r="P7" s="6" t="str"/>
+      <x:c r="Q7" s="6" t="str"/>
+      <x:c r="R7" s="6" t="str"/>
+      <x:c r="S7" s="6" t="str"/>
+      <x:c r="T7" s="8"/>
+      <x:c r="U7" s="8"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="str">
+        <x:v>manual-06</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str"/>
+      <x:c r="D8" s="6" t="n">
+        <x:v>29.5</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="n">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="n">
+        <x:v>14990000</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="n">
+        <x:v>14100000</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I8" s="7"/>
+      <x:c r="J8" s="6"/>
+      <x:c r="K8" s="6" t="str">
+        <x:v>11 из 12</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="str"/>
+      <x:c r="M8" s="6" t="n">
+        <x:v>2025</x:v>
+      </x:c>
+      <x:c r="N8" s="6"/>
+      <x:c r="O8" s="6" t="n">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="str"/>
+      <x:c r="Q8" s="6" t="str"/>
+      <x:c r="R8" s="6" t="str"/>
+      <x:c r="S8" s="6" t="str"/>
+      <x:c r="T8" s="8"/>
+      <x:c r="U8" s="8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="str">
+        <x:v>manual-07</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>1-комн. квартира</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="n">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="n">
+        <x:v>23900000</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="n">
+        <x:v>23000000</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>Исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I9" s="7" t="n">
+        <x:v>46227</x:v>
+      </x:c>
+      <x:c r="J9" s="6"/>
+      <x:c r="K9" s="6" t="str">
+        <x:v>7 из 9</x:v>
+      </x:c>
+      <x:c r="L9" s="6" t="str"/>
+      <x:c r="M9" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="N9" s="6"/>
+      <x:c r="O9" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="str"/>
+      <x:c r="Q9" s="6" t="str"/>
+      <x:c r="R9" s="6" t="str"/>
+      <x:c r="S9" s="6" t="str"/>
+      <x:c r="T9" s="8"/>
+      <x:c r="U9" s="8"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="str">
+        <x:v>manual-08</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Улица Маршала Новикова, 9</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str"/>
+      <x:c r="D10" s="6" t="n">
+        <x:v>38.7</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="n">
+        <x:v>46121</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="n">
+        <x:v>12500000</x:v>
+      </x:c>
+      <x:c r="G10" s="8" t="n">
+        <x:v>12300000</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I10" s="7"/>
+      <x:c r="J10" s="6"/>
+      <x:c r="K10" s="6" t="str">
+        <x:v>10 из 12</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="str">
+        <x:v>Панельный</x:v>
+      </x:c>
+      <x:c r="M10" s="6" t="n">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="N10" s="6"/>
+      <x:c r="O10" s="6"/>
+      <x:c r="P10" s="6" t="str"/>
+      <x:c r="Q10" s="6" t="str"/>
+      <x:c r="R10" s="6" t="str"/>
+      <x:c r="S10" s="6" t="str">
+        <x:v>Комендантский проспект 11–15 мин (способ не указан)</x:v>
+      </x:c>
+      <x:c r="T10" s="8"/>
+      <x:c r="U10" s="8"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="str">
+        <x:v>manual-09</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>Улица Орджоникидзе, 6</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str"/>
+      <x:c r="D11" s="6" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="n">
+        <x:v>46138</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="n">
+        <x:v>10990000</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="n">
+        <x:v>10800000</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>Исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I11" s="7" t="n">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J11" s="6"/>
+      <x:c r="K11" s="6" t="str"/>
+      <x:c r="L11" s="6" t="str"/>
+      <x:c r="M11" s="6"/>
+      <x:c r="N11" s="6"/>
+      <x:c r="O11" s="6"/>
+      <x:c r="P11" s="6" t="str"/>
+      <x:c r="Q11" s="6" t="str"/>
+      <x:c r="R11" s="6" t="str"/>
+      <x:c r="S11" s="6" t="str">
+        <x:v>Московская</x:v>
+      </x:c>
+      <x:c r="T11" s="8"/>
+      <x:c r="U11" s="8"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>manual-10</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Улица Орджоникидзе, 39</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str"/>
+      <x:c r="D12" s="6" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="n">
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="F12" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="n">
+        <x:v>12800000</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>Исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I12" s="7" t="n">
+        <x:v>46165</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str"/>
+      <x:c r="L12" s="6" t="str"/>
+      <x:c r="M12" s="6"/>
+      <x:c r="N12" s="6"/>
+      <x:c r="O12" s="6"/>
+      <x:c r="P12" s="6" t="str"/>
+      <x:c r="Q12" s="6" t="str"/>
+      <x:c r="R12" s="6" t="str"/>
+      <x:c r="S12" s="6" t="str">
+        <x:v>Звёздная</x:v>
+      </x:c>
+      <x:c r="T12" s="8"/>
+      <x:c r="U12" s="8"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="str">
+        <x:v>manual-11</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Коломяжский проспект, 13к2</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str"/>
+      <x:c r="D13" s="6" t="n">
+        <x:v>46.7</x:v>
+      </x:c>
+      <x:c r="E13" s="7" t="n">
+        <x:v>46163</x:v>
+      </x:c>
+      <x:c r="F13" s="8" t="n">
+        <x:v>20500000</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="n">
+        <x:v>19990000</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I13" s="7"/>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="6" t="str">
+        <x:v>13 из 25</x:v>
+      </x:c>
+      <x:c r="L13" s="6" t="str"/>
+      <x:c r="M13" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
+      <x:c r="N13" s="6"/>
+      <x:c r="O13" s="6" t="n">
+        <x:v>2.7</x:v>
+      </x:c>
+      <x:c r="P13" s="6" t="str"/>
+      <x:c r="Q13" s="6" t="str"/>
+      <x:c r="R13" s="6" t="str"/>
+      <x:c r="S13" s="6" t="str">
+        <x:v>Пионерская</x:v>
+      </x:c>
+      <x:c r="T13" s="8"/>
+      <x:c r="U13" s="8"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="6" t="str">
+        <x:v>manual-12</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Бухарестская улица, 86</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>2-комн. квартира</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="n">
+        <x:v>44.3</x:v>
+      </x:c>
+      <x:c r="E14" s="7" t="n">
+        <x:v>46166</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="n">
+        <x:v>14000000</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="n">
+        <x:v>13800000</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I14" s="7"/>
+      <x:c r="J14" s="6"/>
+      <x:c r="K14" s="6" t="str">
+        <x:v>8 из 9</x:v>
+      </x:c>
+      <x:c r="L14" s="6" t="str">
+        <x:v>Панельный</x:v>
+      </x:c>
+      <x:c r="M14" s="6" t="n">
+        <x:v>1967</x:v>
+      </x:c>
+      <x:c r="N14" s="6" t="n">
+        <x:v>7.1</x:v>
+      </x:c>
+      <x:c r="O14" s="6" t="n">
+        <x:v>2.6</x:v>
+      </x:c>
+      <x:c r="P14" s="6" t="str">
+        <x:v>Нет</x:v>
+      </x:c>
+      <x:c r="Q14" s="6" t="str">
+        <x:v>Есть</x:v>
+      </x:c>
+      <x:c r="R14" s="6" t="str"/>
+      <x:c r="S14" s="6" t="str">
+        <x:v>Проспект Славы</x:v>
+      </x:c>
+      <x:c r="T14" s="8"/>
+      <x:c r="U14" s="8"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="6" t="str">
+        <x:v>manual-13</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str"/>
+      <x:c r="D15" s="6" t="n">
+        <x:v>30.6</x:v>
+      </x:c>
+      <x:c r="E15" s="7" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="n">
+        <x:v>10500000</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="n">
+        <x:v>10500000</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>Вновь исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I15" s="7" t="n">
+        <x:v>46218</x:v>
+      </x:c>
+      <x:c r="J15" s="6"/>
+      <x:c r="K15" s="6" t="str"/>
+      <x:c r="L15" s="6" t="str"/>
+      <x:c r="M15" s="6"/>
+      <x:c r="N15" s="6"/>
+      <x:c r="O15" s="6"/>
+      <x:c r="P15" s="6" t="str"/>
+      <x:c r="Q15" s="6" t="str"/>
+      <x:c r="R15" s="6" t="str"/>
+      <x:c r="S15" s="6" t="str">
+        <x:v>Академическая</x:v>
+      </x:c>
+      <x:c r="T15" s="8"/>
+      <x:c r="U15" s="8"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="str">
+        <x:v>manual-14</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>Проспект Тореза, 102</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>Евротрёшка</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="n">
+        <x:v>51.5</x:v>
+      </x:c>
+      <x:c r="E16" s="7" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="F16" s="8" t="n">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="n">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="str">
+        <x:v>Закрылось; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I16" s="7" t="n">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J16" s="6"/>
+      <x:c r="K16" s="6" t="str"/>
+      <x:c r="L16" s="6" t="str"/>
+      <x:c r="M16" s="6"/>
+      <x:c r="N16" s="6"/>
+      <x:c r="O16" s="6"/>
+      <x:c r="P16" s="6" t="str"/>
+      <x:c r="Q16" s="6" t="str"/>
+      <x:c r="R16" s="6" t="str"/>
+      <x:c r="S16" s="6" t="str">
+        <x:v>Удельная</x:v>
+      </x:c>
+      <x:c r="T16" s="8"/>
+      <x:c r="U16" s="8"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="6" t="str">
+        <x:v>manual-15</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str"/>
+      <x:c r="D17" s="6" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="7" t="n">
+        <x:v>46187</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="n">
+        <x:v>29000000</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="n">
+        <x:v>28500000</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I17" s="7"/>
+      <x:c r="J17" s="6"/>
+      <x:c r="K17" s="6" t="str"/>
+      <x:c r="L17" s="6" t="str"/>
+      <x:c r="M17" s="6"/>
+      <x:c r="N17" s="6"/>
+      <x:c r="O17" s="6"/>
+      <x:c r="P17" s="6" t="str"/>
+      <x:c r="Q17" s="6" t="str"/>
+      <x:c r="R17" s="6" t="str"/>
+      <x:c r="S17" s="6" t="str">
+        <x:v>Парк Победы</x:v>
+      </x:c>
+      <x:c r="T17" s="8"/>
+      <x:c r="U17" s="8"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="6" t="str">
+        <x:v>manual-16</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>Проспект Космонавтов, 92</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str"/>
+      <x:c r="D18" s="6" t="n">
+        <x:v>33.6</x:v>
+      </x:c>
+      <x:c r="E18" s="7" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="F18" s="8" t="n">
+        <x:v>11800000</x:v>
+      </x:c>
+      <x:c r="G18" s="8" t="n">
+        <x:v>11600000</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I18" s="7"/>
+      <x:c r="J18" s="6"/>
+      <x:c r="K18" s="6" t="str">
+        <x:v>4 из 9</x:v>
+      </x:c>
+      <x:c r="L18" s="6" t="str">
+        <x:v>Кирпичный</x:v>
+      </x:c>
+      <x:c r="M18" s="6" t="n">
+        <x:v>1966</x:v>
+      </x:c>
+      <x:c r="N18" s="6" t="n">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="O18" s="6" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="P18" s="6" t="str">
+        <x:v>Есть</x:v>
+      </x:c>
+      <x:c r="Q18" s="6" t="str">
+        <x:v>Есть</x:v>
+      </x:c>
+      <x:c r="R18" s="6" t="str">
+        <x:v>Есть</x:v>
+      </x:c>
+      <x:c r="S18" s="6" t="str">
+        <x:v>Звёздная 12 мин пешком</x:v>
+      </x:c>
+      <x:c r="T18" s="8"/>
+      <x:c r="U18" s="8"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="6" t="str">
+        <x:v>manual-17</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Адрес не указан (метро Пионерская)</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>2-комн. квартира</x:v>
+      </x:c>
+      <x:c r="D19" s="6" t="n">
+        <x:v>50.2</x:v>
+      </x:c>
+      <x:c r="E19" s="7" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="n">
+        <x:v>15990000</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="n">
+        <x:v>15990000</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="str">
+        <x:v>Статус не указан</x:v>
+      </x:c>
+      <x:c r="I19" s="7"/>
+      <x:c r="J19" s="6"/>
+      <x:c r="K19" s="6" t="str">
+        <x:v>8 из 9</x:v>
+      </x:c>
+      <x:c r="L19" s="6" t="str">
+        <x:v>Панельный</x:v>
+      </x:c>
+      <x:c r="M19" s="6" t="n">
+        <x:v>1973</x:v>
+      </x:c>
+      <x:c r="N19" s="6" t="n">
+        <x:v>6.8</x:v>
+      </x:c>
+      <x:c r="O19" s="6"/>
+      <x:c r="P19" s="6" t="str"/>
+      <x:c r="Q19" s="6" t="str"/>
+      <x:c r="R19" s="6" t="str"/>
+      <x:c r="S19" s="6" t="str">
+        <x:v>Пионерская 11–15 мин (способ не указан)</x:v>
+      </x:c>
+      <x:c r="T19" s="8"/>
+      <x:c r="U19" s="8"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>manual-18</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Адрес не указан (метро Звёздная)</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>2-комн. квартира</x:v>
+      </x:c>
+      <x:c r="D20" s="6" t="n">
+        <x:v>49.2</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="F20" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="str">
+        <x:v>Исчезло; продажа не подтверждена</x:v>
+      </x:c>
+      <x:c r="I20" s="7" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="J20" s="6"/>
+      <x:c r="K20" s="6" t="str">
+        <x:v>2 из 5</x:v>
+      </x:c>
+      <x:c r="L20" s="6" t="str">
+        <x:v>Панельный</x:v>
+      </x:c>
+      <x:c r="M20" s="6" t="n">
+        <x:v>1965</x:v>
+      </x:c>
+      <x:c r="N20" s="6"/>
+      <x:c r="O20" s="6"/>
+      <x:c r="P20" s="6" t="str"/>
+      <x:c r="Q20" s="6" t="str"/>
+      <x:c r="R20" s="6" t="str">
+        <x:v>Нет</x:v>
+      </x:c>
+      <x:c r="S20" s="6" t="str">
+        <x:v>Звёздная</x:v>
+      </x:c>
+      <x:c r="T20" s="8"/>
+      <x:c r="U20" s="8"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:U1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="50" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="11" t="str">
+        <x:v>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — цены и события со слов пользователя; некоторые даты неизвестны.</x:v>
+      </x:c>
+      <x:c r="B1" s="11"/>
+      <x:c r="C1" s="11"/>
+      <x:c r="D1" s="11"/>
+      <x:c r="E1" s="11"/>
+      <x:c r="F1" s="11"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="12" t="str">
+        <x:v>ID заметки</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str">
+        <x:v>Адрес</x:v>
+      </x:c>
+      <x:c r="C2" s="12" t="str">
+        <x:v>Дата</x:v>
+      </x:c>
+      <x:c r="D2" s="12" t="str">
+        <x:v>Цена, ₽</x:v>
+      </x:c>
+      <x:c r="E2" s="12" t="str">
+        <x:v>Тип записи</x:v>
+      </x:c>
+      <x:c r="F2" s="12" t="str">
+        <x:v>Примечание</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="6" t="str">
+        <x:v>manual-01</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C3" s="7" t="n">
+        <x:v>46048</x:v>
+      </x:c>
+      <x:c r="D3" s="8" t="n">
+        <x:v>9990000</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="6" t="str">
+        <x:v>manual-01</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C4" s="7" t="n">
+        <x:v>46119</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="n">
+        <x:v>9600000</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>Названа ценой продажи</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="6" t="str">
+        <x:v>manual-02</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="n">
+        <x:v>46067</x:v>
+      </x:c>
+      <x:c r="D5" s="8" t="n">
+        <x:v>11700000</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="6" t="str">
+        <x:v>manual-02</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="n">
+        <x:v>46129</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="n">
+        <x:v>11500000</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="6" t="str">
+        <x:v>manual-02</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C7" s="7"/>
+      <x:c r="D7" s="8"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>17.04 перевыложили объявление</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="str">
+        <x:v>manual-03</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Стародеревенская улица, 6</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="n">
+        <x:v>46095</x:v>
+      </x:c>
+      <x:c r="D8" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="str">
+        <x:v>manual-03</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Стародеревенская улица, 6</x:v>
+      </x:c>
+      <x:c r="C9" s="7"/>
+      <x:c r="D9" s="8" t="n">
+        <x:v>12800000</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>Дата не указана</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="str">
+        <x:v>manual-03</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Стародеревенская улица, 6</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="n">
+        <x:v>46206</x:v>
+      </x:c>
+      <x:c r="D10" s="8" t="n">
+        <x:v>12500000</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="str">
+        <x:v>manual-03</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>Стародеревенская улица, 6</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="D11" s="8" t="n">
+        <x:v>12300000</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="str">
+        <x:v>manual-03</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Стародеревенская улица, 6</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="n">
+        <x:v>46227</x:v>
+      </x:c>
+      <x:c r="D12" s="8" t="n">
+        <x:v>12500000</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C13" s="7" t="n">
+        <x:v>46076</x:v>
+      </x:c>
+      <x:c r="D13" s="8" t="n">
+        <x:v>22990000</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="n">
+        <x:v>46118</x:v>
+      </x:c>
+      <x:c r="D14" s="8" t="n">
+        <x:v>22500000</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C15" s="7"/>
+      <x:c r="D15" s="8" t="n">
+        <x:v>23230000</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>Перевыложили, точная дата не указана</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="n">
+        <x:v>46153</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="n">
+        <x:v>23000000</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C17" s="7" t="n">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="n">
+        <x:v>22500000</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C18" s="7" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="D18" s="8" t="n">
+        <x:v>22000000</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C19" s="7"/>
+      <x:c r="D19" s="8"/>
+      <x:c r="E19" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str">
+        <x:v>25.04 исчезло</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C20" s="7"/>
+      <x:c r="D20" s="8"/>
+      <x:c r="E20" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F20" s="6" t="str">
+        <x:v>После 25.04 перевыложили за 23 230 000 ₽</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="6" t="str">
+        <x:v>manual-04</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C21" s="7"/>
+      <x:c r="D21" s="8"/>
+      <x:c r="E21" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str">
+        <x:v>25.06 продано — со слов пользователя</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="6" t="str">
+        <x:v>manual-05</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C22" s="7" t="n">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="n">
+        <x:v>17400000</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="6" t="str">
+        <x:v>manual-05</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C23" s="7" t="n">
+        <x:v>46132</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="n">
+        <x:v>16990000</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="6" t="str">
+        <x:v>manual-06</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C24" s="7" t="n">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="n">
+        <x:v>14990000</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="6" t="str">
+        <x:v>manual-06</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C25" s="7" t="n">
+        <x:v>46132</x:v>
+      </x:c>
+      <x:c r="D25" s="8" t="n">
+        <x:v>14800000</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="6" t="str">
+        <x:v>manual-06</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C26" s="7" t="n">
+        <x:v>46190</x:v>
+      </x:c>
+      <x:c r="D26" s="8" t="n">
+        <x:v>14600000</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="6" t="str">
+        <x:v>manual-06</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C27" s="7" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="D27" s="8" t="n">
+        <x:v>14300000</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="6" t="str">
+        <x:v>manual-06</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C28" s="7" t="n">
+        <x:v>46231</x:v>
+      </x:c>
+      <x:c r="D28" s="8" t="n">
+        <x:v>14100000</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="6" t="str">
+        <x:v>manual-07</x:v>
+      </x:c>
+      <x:c r="B29" s="6" t="str">
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C29" s="7" t="n">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="D29" s="8" t="n">
+        <x:v>23900000</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="str"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="6" t="str">
+        <x:v>manual-07</x:v>
+      </x:c>
+      <x:c r="B30" s="6" t="str">
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C30" s="7"/>
+      <x:c r="D30" s="8" t="n">
+        <x:v>23500000</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="str">
+        <x:v>Дата не указана</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="6" t="str">
+        <x:v>manual-07</x:v>
+      </x:c>
+      <x:c r="B31" s="6" t="str">
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C31" s="7" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="D31" s="8" t="n">
+        <x:v>23000000</x:v>
+      </x:c>
+      <x:c r="E31" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="6" t="str">
+        <x:v>manual-08</x:v>
+      </x:c>
+      <x:c r="B32" s="6" t="str">
+        <x:v>Улица Маршала Новикова, 9</x:v>
+      </x:c>
+      <x:c r="C32" s="7" t="n">
+        <x:v>46121</x:v>
+      </x:c>
+      <x:c r="D32" s="8" t="n">
+        <x:v>12500000</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="6" t="str">
+        <x:v>manual-08</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>Улица Маршала Новикова, 9</x:v>
+      </x:c>
+      <x:c r="C33" s="7" t="n">
+        <x:v>46214</x:v>
+      </x:c>
+      <x:c r="D33" s="8" t="n">
+        <x:v>12300000</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="6" t="str">
+        <x:v>manual-09</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>Улица Орджоникидзе, 6</x:v>
+      </x:c>
+      <x:c r="C34" s="7" t="n">
+        <x:v>46138</x:v>
+      </x:c>
+      <x:c r="D34" s="8" t="n">
+        <x:v>10990000</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="str"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="6" t="str">
+        <x:v>manual-09</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>Улица Орджоникидзе, 6</x:v>
+      </x:c>
+      <x:c r="C35" s="7" t="n">
+        <x:v>46168</x:v>
+      </x:c>
+      <x:c r="D35" s="8" t="n">
+        <x:v>10800000</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="str"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="6" t="str">
+        <x:v>manual-10</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>Улица Орджоникидзе, 39</x:v>
+      </x:c>
+      <x:c r="C36" s="7" t="n">
+        <x:v>46142</x:v>
+      </x:c>
+      <x:c r="D36" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="E36" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="6" t="str">
+        <x:v>manual-10</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>Улица Орджоникидзе, 39</x:v>
+      </x:c>
+      <x:c r="C37" s="7"/>
+      <x:c r="D37" s="8" t="n">
+        <x:v>12800000</x:v>
+      </x:c>
+      <x:c r="E37" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>Дата не указана</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="6" t="str">
+        <x:v>manual-11</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>Коломяжский проспект, 13к2</x:v>
+      </x:c>
+      <x:c r="C38" s="7" t="n">
+        <x:v>46163</x:v>
+      </x:c>
+      <x:c r="D38" s="8" t="n">
+        <x:v>20500000</x:v>
+      </x:c>
+      <x:c r="E38" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="6" t="str">
+        <x:v>manual-11</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>Коломяжский проспект, 13к2</x:v>
+      </x:c>
+      <x:c r="C39" s="7" t="n">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="D39" s="8" t="n">
+        <x:v>19990000</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="6" t="str">
+        <x:v>manual-12</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>Бухарестская улица, 86</x:v>
+      </x:c>
+      <x:c r="C40" s="7" t="n">
+        <x:v>46166</x:v>
+      </x:c>
+      <x:c r="D40" s="8" t="n">
+        <x:v>14000000</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="6" t="str">
+        <x:v>manual-12</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>Бухарестская улица, 86</x:v>
+      </x:c>
+      <x:c r="C41" s="7" t="n">
+        <x:v>46217</x:v>
+      </x:c>
+      <x:c r="D41" s="8" t="n">
+        <x:v>13800000</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="6" t="str">
+        <x:v>manual-13</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C42" s="7" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="D42" s="8" t="n">
+        <x:v>10500000</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="6" t="str">
+        <x:v>manual-13</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C43" s="7"/>
+      <x:c r="D43" s="8"/>
+      <x:c r="E43" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>06.07 продано — со слов пользователя</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="6" t="str">
+        <x:v>manual-13</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C44" s="7"/>
+      <x:c r="D44" s="8"/>
+      <x:c r="E44" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>Затем вновь появилось, дата не указана</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="6" t="str">
+        <x:v>manual-13</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C45" s="7"/>
+      <x:c r="D45" s="8"/>
+      <x:c r="E45" s="6" t="str">
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>15.07 вновь исчезло</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="6" t="str">
+        <x:v>manual-14</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>Проспект Тореза, 102</x:v>
+      </x:c>
+      <x:c r="C46" s="7" t="n">
+        <x:v>46184</x:v>
+      </x:c>
+      <x:c r="D46" s="8" t="n">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="E46" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="str"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="6" t="str">
+        <x:v>manual-15</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C47" s="7" t="n">
+        <x:v>46187</x:v>
+      </x:c>
+      <x:c r="D47" s="8" t="n">
+        <x:v>29000000</x:v>
+      </x:c>
+      <x:c r="E47" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="6" t="str">
+        <x:v>manual-15</x:v>
+      </x:c>
+      <x:c r="B48" s="6" t="str">
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C48" s="7" t="n">
+        <x:v>46206</x:v>
+      </x:c>
+      <x:c r="D48" s="8" t="n">
+        <x:v>28500000</x:v>
+      </x:c>
+      <x:c r="E48" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F48" s="6" t="str"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="6" t="str">
+        <x:v>manual-16</x:v>
+      </x:c>
+      <x:c r="B49" s="6" t="str">
+        <x:v>Проспект Космонавтов, 92</x:v>
+      </x:c>
+      <x:c r="C49" s="7" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="D49" s="8" t="n">
+        <x:v>11800000</x:v>
+      </x:c>
+      <x:c r="E49" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F49" s="6" t="str"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="6" t="str">
+        <x:v>manual-16</x:v>
+      </x:c>
+      <x:c r="B50" s="6" t="str">
+        <x:v>Проспект Космонавтов, 92</x:v>
+      </x:c>
+      <x:c r="C50" s="7" t="n">
+        <x:v>46213</x:v>
+      </x:c>
+      <x:c r="D50" s="8" t="n">
+        <x:v>11600000</x:v>
+      </x:c>
+      <x:c r="E50" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F50" s="6" t="str"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="6" t="str">
+        <x:v>manual-17</x:v>
+      </x:c>
+      <x:c r="B51" s="6" t="str">
+        <x:v>Адрес не указан (метро Пионерская)</x:v>
+      </x:c>
+      <x:c r="C51" s="7" t="n">
+        <x:v>46212</x:v>
+      </x:c>
+      <x:c r="D51" s="8" t="n">
+        <x:v>15990000</x:v>
+      </x:c>
+      <x:c r="E51" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F51" s="6" t="str"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="6" t="str">
+        <x:v>manual-18</x:v>
+      </x:c>
+      <x:c r="B52" s="6" t="str">
+        <x:v>Адрес не указан (метро Звёздная)</x:v>
+      </x:c>
+      <x:c r="C52" s="7" t="n">
+        <x:v>46220</x:v>
+      </x:c>
+      <x:c r="D52" s="8" t="n">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="E52" s="6" t="str">
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F52" s="6" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="Rcadb430f078240e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История цен" sheetId="2" r:id="R6d54ac61e1b147d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Старый архив" sheetId="3" r:id="Ra52960e56ed840c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены старого архива" sheetId="4" r:id="R24dff7f110a84da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="R33050958525f4235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История цен" sheetId="2" r:id="R1ada1ce07b914ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Старый архив" sheetId="3" r:id="Ra9eedd37419c4984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены старого архива" sheetId="4" r:id="Rb21b1a79c38c474d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1324,7 +1324,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — из заметок пользователя, не сверены с Цианом. Исчезновение объявления не подтверждает продажу.</x:v>
+        <x:v>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — сведения о продаже со слов пользователя, не сверены с Цианом. Дата исчезновения не равна дате сделки.</x:v>
       </x:c>
       <x:c r="B1" s="11"/>
       <x:c r="C1" s="11"/>
@@ -1433,7 +1433,7 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>Цена продажи — со слов пользователя</x:v>
+        <x:v>Продано — со слов пользователя</x:v>
       </x:c>
       <x:c r="I3" s="7" t="n">
         <x:v>46119</x:v>
@@ -1478,11 +1478,9 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>Исчезло; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I4" s="7" t="n">
-        <x:v>46139</x:v>
-      </x:c>
+        <x:v>Продано — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I4" s="7"/>
       <x:c r="J4" s="6" t="n">
         <x:v>73</x:v>
       </x:c>
@@ -1500,77 +1498,69 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="6" t="str">
-        <x:v>manual-03</x:v>
+        <x:v>manual-04</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Стародеревенская улица, 6</x:v>
+        <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str"/>
       <x:c r="D5" s="6" t="n">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E5" s="7" t="n">
-        <x:v>46095</x:v>
+        <x:v>46076</x:v>
       </x:c>
       <x:c r="F5" s="8" t="n">
-        <x:v>12990000</x:v>
+        <x:v>22990000</x:v>
       </x:c>
       <x:c r="G5" s="8" t="n">
-        <x:v>12500000</x:v>
+        <x:v>22000000</x:v>
       </x:c>
       <x:c r="H5" s="6" t="str">
-        <x:v>Статус не указан</x:v>
-      </x:c>
-      <x:c r="I5" s="7"/>
+        <x:v>Продано 25.06 — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I5" s="7" t="n">
+        <x:v>46198</x:v>
+      </x:c>
       <x:c r="J5" s="6"/>
-      <x:c r="K5" s="6" t="str">
-        <x:v>17 из 17</x:v>
-      </x:c>
-      <x:c r="L5" s="6" t="str">
-        <x:v>Панельный</x:v>
-      </x:c>
-      <x:c r="M5" s="6" t="n">
-        <x:v>1991</x:v>
-      </x:c>
+      <x:c r="K5" s="6" t="str"/>
+      <x:c r="L5" s="6" t="str"/>
+      <x:c r="M5" s="6"/>
       <x:c r="N5" s="6"/>
       <x:c r="O5" s="6"/>
-      <x:c r="P5" s="6" t="str">
-        <x:v>Есть</x:v>
-      </x:c>
+      <x:c r="P5" s="6" t="str"/>
       <x:c r="Q5" s="6" t="str"/>
       <x:c r="R5" s="6" t="str"/>
       <x:c r="S5" s="6" t="str">
-        <x:v>Старая Деревня 11–15 мин (способ не указан)</x:v>
+        <x:v>Электросила</x:v>
       </x:c>
       <x:c r="T5" s="8"/>
       <x:c r="U5" s="8"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="6" t="str">
-        <x:v>manual-04</x:v>
+        <x:v>manual-05</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
+        <x:v>Проспект Энгельса, 31</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str"/>
       <x:c r="D6" s="6" t="n">
-        <x:v>45</x:v>
+        <x:v>37.8</x:v>
       </x:c>
       <x:c r="E6" s="7" t="n">
-        <x:v>46076</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="F6" s="8" t="n">
-        <x:v>22990000</x:v>
+        <x:v>17400000</x:v>
       </x:c>
       <x:c r="G6" s="8" t="n">
-        <x:v>22000000</x:v>
+        <x:v>16990000</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
-        <x:v>Продано 25.06 — со слов пользователя</x:v>
-      </x:c>
-      <x:c r="I6" s="7" t="n">
-        <x:v>46198</x:v>
-      </x:c>
+        <x:v>Продано — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I6" s="7"/>
       <x:c r="J6" s="6"/>
       <x:c r="K6" s="6" t="str"/>
       <x:c r="L6" s="6" t="str"/>
@@ -1580,44 +1570,48 @@
       <x:c r="P6" s="6" t="str"/>
       <x:c r="Q6" s="6" t="str"/>
       <x:c r="R6" s="6" t="str"/>
-      <x:c r="S6" s="6" t="str">
-        <x:v>Электросила</x:v>
-      </x:c>
+      <x:c r="S6" s="6" t="str"/>
       <x:c r="T6" s="8"/>
       <x:c r="U6" s="8"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="6" t="str">
-        <x:v>manual-05</x:v>
+        <x:v>manual-07</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="str"/>
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>1-комн. квартира</x:v>
+      </x:c>
       <x:c r="D7" s="6" t="n">
-        <x:v>37.8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E7" s="7" t="n">
-        <x:v>46107</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="F7" s="8" t="n">
-        <x:v>17400000</x:v>
+        <x:v>23900000</x:v>
       </x:c>
       <x:c r="G7" s="8" t="n">
-        <x:v>16990000</x:v>
+        <x:v>23000000</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
-        <x:v>Исчезло; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I7" s="7" t="n">
-        <x:v>46181</x:v>
-      </x:c>
+        <x:v>Продано — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I7" s="7"/>
       <x:c r="J7" s="6"/>
-      <x:c r="K7" s="6" t="str"/>
+      <x:c r="K7" s="6" t="str">
+        <x:v>7 из 9</x:v>
+      </x:c>
       <x:c r="L7" s="6" t="str"/>
-      <x:c r="M7" s="6"/>
+      <x:c r="M7" s="6" t="n">
+        <x:v>2024</x:v>
+      </x:c>
       <x:c r="N7" s="6"/>
-      <x:c r="O7" s="6"/>
+      <x:c r="O7" s="6" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="P7" s="6" t="str"/>
       <x:c r="Q7" s="6" t="str"/>
       <x:c r="R7" s="6" t="str"/>
@@ -1627,165 +1621,149 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="str">
-        <x:v>manual-06</x:v>
+        <x:v>manual-09</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
+        <x:v>Улица Орджоникидзе, 6</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str"/>
       <x:c r="D8" s="6" t="n">
-        <x:v>29.5</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E8" s="7" t="n">
-        <x:v>46107</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="F8" s="8" t="n">
-        <x:v>14990000</x:v>
+        <x:v>10990000</x:v>
       </x:c>
       <x:c r="G8" s="8" t="n">
-        <x:v>14100000</x:v>
+        <x:v>10800000</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>Статус не указан</x:v>
+        <x:v>Продано — со слов пользователя</x:v>
       </x:c>
       <x:c r="I8" s="7"/>
       <x:c r="J8" s="6"/>
-      <x:c r="K8" s="6" t="str">
-        <x:v>11 из 12</x:v>
-      </x:c>
+      <x:c r="K8" s="6" t="str"/>
       <x:c r="L8" s="6" t="str"/>
-      <x:c r="M8" s="6" t="n">
-        <x:v>2025</x:v>
-      </x:c>
+      <x:c r="M8" s="6"/>
       <x:c r="N8" s="6"/>
-      <x:c r="O8" s="6" t="n">
-        <x:v>2.8</x:v>
-      </x:c>
+      <x:c r="O8" s="6"/>
       <x:c r="P8" s="6" t="str"/>
       <x:c r="Q8" s="6" t="str"/>
       <x:c r="R8" s="6" t="str"/>
-      <x:c r="S8" s="6" t="str"/>
+      <x:c r="S8" s="6" t="str">
+        <x:v>Московская</x:v>
+      </x:c>
       <x:c r="T8" s="8"/>
       <x:c r="U8" s="8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6" t="str">
-        <x:v>manual-07</x:v>
+        <x:v>manual-10</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>Улица Стахановцев, 1</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>1-комн. квартира</x:v>
-      </x:c>
+        <x:v>Улица Орджоникидзе, 39</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str"/>
       <x:c r="D9" s="6" t="n">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E9" s="7" t="n">
-        <x:v>46112</x:v>
+        <x:v>46142</x:v>
       </x:c>
       <x:c r="F9" s="8" t="n">
-        <x:v>23900000</x:v>
+        <x:v>12990000</x:v>
       </x:c>
       <x:c r="G9" s="8" t="n">
-        <x:v>23000000</x:v>
+        <x:v>12800000</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>Исчезло; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I9" s="7" t="n">
-        <x:v>46227</x:v>
-      </x:c>
-      <x:c r="J9" s="6"/>
-      <x:c r="K9" s="6" t="str">
-        <x:v>7 из 9</x:v>
-      </x:c>
+        <x:v>Продано — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I9" s="7"/>
+      <x:c r="J9" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str"/>
       <x:c r="L9" s="6" t="str"/>
-      <x:c r="M9" s="6" t="n">
-        <x:v>2024</x:v>
-      </x:c>
+      <x:c r="M9" s="6"/>
       <x:c r="N9" s="6"/>
-      <x:c r="O9" s="6" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="O9" s="6"/>
       <x:c r="P9" s="6" t="str"/>
       <x:c r="Q9" s="6" t="str"/>
       <x:c r="R9" s="6" t="str"/>
-      <x:c r="S9" s="6" t="str"/>
+      <x:c r="S9" s="6" t="str">
+        <x:v>Звёздная</x:v>
+      </x:c>
       <x:c r="T9" s="8"/>
       <x:c r="U9" s="8"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6" t="str">
-        <x:v>manual-08</x:v>
+        <x:v>manual-13</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
-        <x:v>Улица Маршала Новикова, 9</x:v>
+        <x:v>Проспект Науки, 14к1</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str"/>
       <x:c r="D10" s="6" t="n">
-        <x:v>38.7</x:v>
+        <x:v>30.6</x:v>
       </x:c>
       <x:c r="E10" s="7" t="n">
-        <x:v>46121</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="F10" s="8" t="n">
-        <x:v>12500000</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="G10" s="8" t="n">
-        <x:v>12300000</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>Статус не указан</x:v>
+        <x:v>Продано — со слов пользователя</x:v>
       </x:c>
       <x:c r="I10" s="7"/>
       <x:c r="J10" s="6"/>
-      <x:c r="K10" s="6" t="str">
-        <x:v>10 из 12</x:v>
-      </x:c>
-      <x:c r="L10" s="6" t="str">
-        <x:v>Панельный</x:v>
-      </x:c>
-      <x:c r="M10" s="6" t="n">
-        <x:v>1986</x:v>
-      </x:c>
+      <x:c r="K10" s="6" t="str"/>
+      <x:c r="L10" s="6" t="str"/>
+      <x:c r="M10" s="6"/>
       <x:c r="N10" s="6"/>
       <x:c r="O10" s="6"/>
       <x:c r="P10" s="6" t="str"/>
       <x:c r="Q10" s="6" t="str"/>
       <x:c r="R10" s="6" t="str"/>
       <x:c r="S10" s="6" t="str">
-        <x:v>Комендантский проспект 11–15 мин (способ не указан)</x:v>
+        <x:v>Академическая</x:v>
       </x:c>
       <x:c r="T10" s="8"/>
       <x:c r="U10" s="8"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="6" t="str">
-        <x:v>manual-09</x:v>
+        <x:v>manual-14</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>Улица Орджоникидзе, 6</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str"/>
+        <x:v>Проспект Тореза, 102</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>Евротрёшка</x:v>
+      </x:c>
       <x:c r="D11" s="6" t="n">
-        <x:v>30</x:v>
+        <x:v>51.5</x:v>
       </x:c>
       <x:c r="E11" s="7" t="n">
-        <x:v>46138</x:v>
+        <x:v>46184</x:v>
       </x:c>
       <x:c r="F11" s="8" t="n">
-        <x:v>10990000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="G11" s="8" t="n">
-        <x:v>10800000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>Исчезло; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I11" s="7" t="n">
-        <x:v>46196</x:v>
-      </x:c>
+        <x:v>Продано — со слов пользователя</x:v>
+      </x:c>
+      <x:c r="I11" s="7"/>
       <x:c r="J11" s="6"/>
       <x:c r="K11" s="6" t="str"/>
       <x:c r="L11" s="6" t="str"/>
@@ -1796,40 +1774,38 @@
       <x:c r="Q11" s="6" t="str"/>
       <x:c r="R11" s="6" t="str"/>
       <x:c r="S11" s="6" t="str">
-        <x:v>Московская</x:v>
+        <x:v>Удельная</x:v>
       </x:c>
       <x:c r="T11" s="8"/>
       <x:c r="U11" s="8"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="str">
-        <x:v>manual-10</x:v>
+        <x:v>manual-15</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>Улица Орджоникидзе, 39</x:v>
+        <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str"/>
       <x:c r="D12" s="6" t="n">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="7" t="n">
-        <x:v>46142</x:v>
+        <x:v>46187</x:v>
       </x:c>
       <x:c r="F12" s="8" t="n">
-        <x:v>12990000</x:v>
+        <x:v>29000000</x:v>
       </x:c>
       <x:c r="G12" s="8" t="n">
-        <x:v>12800000</x:v>
+        <x:v>28000000</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>Исчезло; продажа не подтверждена</x:v>
+        <x:v>Продано — со слов пользователя</x:v>
       </x:c>
       <x:c r="I12" s="7" t="n">
-        <x:v>46165</x:v>
-      </x:c>
-      <x:c r="J12" s="6" t="n">
-        <x:v>24</x:v>
-      </x:c>
+        <x:v>46308</x:v>
+      </x:c>
+      <x:c r="J12" s="6"/>
       <x:c r="K12" s="6" t="str"/>
       <x:c r="L12" s="6" t="str"/>
       <x:c r="M12" s="6"/>
@@ -1839,386 +1815,218 @@
       <x:c r="Q12" s="6" t="str"/>
       <x:c r="R12" s="6" t="str"/>
       <x:c r="S12" s="6" t="str">
-        <x:v>Звёздная</x:v>
+        <x:v>Парк Победы</x:v>
       </x:c>
       <x:c r="T12" s="8"/>
       <x:c r="U12" s="8"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="6" t="str">
-        <x:v>manual-11</x:v>
+        <x:v>manual-18</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>Коломяжский проспект, 13к2</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="str"/>
+        <x:v>Адрес не указан (метро Звёздная)</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>2-комн. квартира</x:v>
+      </x:c>
       <x:c r="D13" s="6" t="n">
-        <x:v>46.7</x:v>
+        <x:v>49.2</x:v>
       </x:c>
       <x:c r="E13" s="7" t="n">
-        <x:v>46163</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="F13" s="8" t="n">
-        <x:v>20500000</x:v>
+        <x:v>12990000</x:v>
       </x:c>
       <x:c r="G13" s="8" t="n">
-        <x:v>19990000</x:v>
+        <x:v>12990000</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>Статус не указан</x:v>
+        <x:v>Продано — со слов пользователя</x:v>
       </x:c>
       <x:c r="I13" s="7"/>
       <x:c r="J13" s="6"/>
       <x:c r="K13" s="6" t="str">
-        <x:v>13 из 25</x:v>
-      </x:c>
-      <x:c r="L13" s="6" t="str"/>
+        <x:v>2 из 5</x:v>
+      </x:c>
+      <x:c r="L13" s="6" t="str">
+        <x:v>Панельный</x:v>
+      </x:c>
       <x:c r="M13" s="6" t="n">
-        <x:v>2024</x:v>
+        <x:v>1965</x:v>
       </x:c>
       <x:c r="N13" s="6"/>
-      <x:c r="O13" s="6" t="n">
-        <x:v>2.7</x:v>
-      </x:c>
+      <x:c r="O13" s="6"/>
       <x:c r="P13" s="6" t="str"/>
       <x:c r="Q13" s="6" t="str"/>
-      <x:c r="R13" s="6" t="str"/>
+      <x:c r="R13" s="6" t="str">
+        <x:v>Нет</x:v>
+      </x:c>
       <x:c r="S13" s="6" t="str">
-        <x:v>Пионерская</x:v>
+        <x:v>Звёздная</x:v>
       </x:c>
       <x:c r="T13" s="8"/>
       <x:c r="U13" s="8"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="6" t="str">
-        <x:v>manual-12</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="str">
-        <x:v>Бухарестская улица, 86</x:v>
-      </x:c>
-      <x:c r="C14" s="6" t="str">
-        <x:v>2-комн. квартира</x:v>
-      </x:c>
-      <x:c r="D14" s="6" t="n">
-        <x:v>44.3</x:v>
-      </x:c>
-      <x:c r="E14" s="7" t="n">
-        <x:v>46166</x:v>
-      </x:c>
-      <x:c r="F14" s="8" t="n">
-        <x:v>14000000</x:v>
-      </x:c>
-      <x:c r="G14" s="8" t="n">
-        <x:v>13800000</x:v>
-      </x:c>
-      <x:c r="H14" s="6" t="str">
-        <x:v>Статус не указан</x:v>
-      </x:c>
+      <x:c r="A14" s="6"/>
+      <x:c r="B14" s="6"/>
+      <x:c r="C14" s="6"/>
+      <x:c r="D14" s="6"/>
+      <x:c r="E14" s="7"/>
+      <x:c r="F14" s="8"/>
+      <x:c r="G14" s="8"/>
+      <x:c r="H14" s="6"/>
       <x:c r="I14" s="7"/>
       <x:c r="J14" s="6"/>
-      <x:c r="K14" s="6" t="str">
-        <x:v>8 из 9</x:v>
-      </x:c>
-      <x:c r="L14" s="6" t="str">
-        <x:v>Панельный</x:v>
-      </x:c>
-      <x:c r="M14" s="6" t="n">
-        <x:v>1967</x:v>
-      </x:c>
-      <x:c r="N14" s="6" t="n">
-        <x:v>7.1</x:v>
-      </x:c>
-      <x:c r="O14" s="6" t="n">
-        <x:v>2.6</x:v>
-      </x:c>
-      <x:c r="P14" s="6" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="Q14" s="6" t="str">
-        <x:v>Есть</x:v>
-      </x:c>
-      <x:c r="R14" s="6" t="str"/>
-      <x:c r="S14" s="6" t="str">
-        <x:v>Проспект Славы</x:v>
-      </x:c>
+      <x:c r="K14" s="6"/>
+      <x:c r="L14" s="6"/>
+      <x:c r="M14" s="6"/>
+      <x:c r="N14" s="6"/>
+      <x:c r="O14" s="6"/>
+      <x:c r="P14" s="6"/>
+      <x:c r="Q14" s="6"/>
+      <x:c r="R14" s="6"/>
+      <x:c r="S14" s="6"/>
       <x:c r="T14" s="8"/>
       <x:c r="U14" s="8"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="6" t="str">
-        <x:v>manual-13</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="str">
-        <x:v>Проспект Науки, 14к1</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="str"/>
-      <x:c r="D15" s="6" t="n">
-        <x:v>30.6</x:v>
-      </x:c>
-      <x:c r="E15" s="7" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="F15" s="8" t="n">
-        <x:v>10500000</x:v>
-      </x:c>
-      <x:c r="G15" s="8" t="n">
-        <x:v>10500000</x:v>
-      </x:c>
-      <x:c r="H15" s="6" t="str">
-        <x:v>Вновь исчезло; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I15" s="7" t="n">
-        <x:v>46218</x:v>
-      </x:c>
+      <x:c r="A15" s="6"/>
+      <x:c r="B15" s="6"/>
+      <x:c r="C15" s="6"/>
+      <x:c r="D15" s="6"/>
+      <x:c r="E15" s="7"/>
+      <x:c r="F15" s="8"/>
+      <x:c r="G15" s="8"/>
+      <x:c r="H15" s="6"/>
+      <x:c r="I15" s="7"/>
       <x:c r="J15" s="6"/>
-      <x:c r="K15" s="6" t="str"/>
-      <x:c r="L15" s="6" t="str"/>
+      <x:c r="K15" s="6"/>
+      <x:c r="L15" s="6"/>
       <x:c r="M15" s="6"/>
       <x:c r="N15" s="6"/>
       <x:c r="O15" s="6"/>
-      <x:c r="P15" s="6" t="str"/>
-      <x:c r="Q15" s="6" t="str"/>
-      <x:c r="R15" s="6" t="str"/>
-      <x:c r="S15" s="6" t="str">
-        <x:v>Академическая</x:v>
-      </x:c>
+      <x:c r="P15" s="6"/>
+      <x:c r="Q15" s="6"/>
+      <x:c r="R15" s="6"/>
+      <x:c r="S15" s="6"/>
       <x:c r="T15" s="8"/>
       <x:c r="U15" s="8"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="6" t="str">
-        <x:v>manual-14</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="str">
-        <x:v>Проспект Тореза, 102</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="str">
-        <x:v>Евротрёшка</x:v>
-      </x:c>
-      <x:c r="D16" s="6" t="n">
-        <x:v>51.5</x:v>
-      </x:c>
-      <x:c r="E16" s="7" t="n">
-        <x:v>46184</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="n">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="G16" s="8" t="n">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="H16" s="6" t="str">
-        <x:v>Закрылось; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I16" s="7" t="n">
-        <x:v>46196</x:v>
-      </x:c>
+      <x:c r="A16" s="6"/>
+      <x:c r="B16" s="6"/>
+      <x:c r="C16" s="6"/>
+      <x:c r="D16" s="6"/>
+      <x:c r="E16" s="7"/>
+      <x:c r="F16" s="8"/>
+      <x:c r="G16" s="8"/>
+      <x:c r="H16" s="6"/>
+      <x:c r="I16" s="7"/>
       <x:c r="J16" s="6"/>
-      <x:c r="K16" s="6" t="str"/>
-      <x:c r="L16" s="6" t="str"/>
+      <x:c r="K16" s="6"/>
+      <x:c r="L16" s="6"/>
       <x:c r="M16" s="6"/>
       <x:c r="N16" s="6"/>
       <x:c r="O16" s="6"/>
-      <x:c r="P16" s="6" t="str"/>
-      <x:c r="Q16" s="6" t="str"/>
-      <x:c r="R16" s="6" t="str"/>
-      <x:c r="S16" s="6" t="str">
-        <x:v>Удельная</x:v>
-      </x:c>
+      <x:c r="P16" s="6"/>
+      <x:c r="Q16" s="6"/>
+      <x:c r="R16" s="6"/>
+      <x:c r="S16" s="6"/>
       <x:c r="T16" s="8"/>
       <x:c r="U16" s="8"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="6" t="str">
-        <x:v>manual-15</x:v>
-      </x:c>
-      <x:c r="B17" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
-      </x:c>
-      <x:c r="C17" s="6" t="str"/>
-      <x:c r="D17" s="6" t="n">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E17" s="7" t="n">
-        <x:v>46187</x:v>
-      </x:c>
-      <x:c r="F17" s="8" t="n">
-        <x:v>29000000</x:v>
-      </x:c>
-      <x:c r="G17" s="8" t="n">
-        <x:v>28500000</x:v>
-      </x:c>
-      <x:c r="H17" s="6" t="str">
-        <x:v>Статус не указан</x:v>
-      </x:c>
+      <x:c r="A17" s="6"/>
+      <x:c r="B17" s="6"/>
+      <x:c r="C17" s="6"/>
+      <x:c r="D17" s="6"/>
+      <x:c r="E17" s="7"/>
+      <x:c r="F17" s="8"/>
+      <x:c r="G17" s="8"/>
+      <x:c r="H17" s="6"/>
       <x:c r="I17" s="7"/>
       <x:c r="J17" s="6"/>
-      <x:c r="K17" s="6" t="str"/>
-      <x:c r="L17" s="6" t="str"/>
+      <x:c r="K17" s="6"/>
+      <x:c r="L17" s="6"/>
       <x:c r="M17" s="6"/>
       <x:c r="N17" s="6"/>
       <x:c r="O17" s="6"/>
-      <x:c r="P17" s="6" t="str"/>
-      <x:c r="Q17" s="6" t="str"/>
-      <x:c r="R17" s="6" t="str"/>
-      <x:c r="S17" s="6" t="str">
-        <x:v>Парк Победы</x:v>
-      </x:c>
+      <x:c r="P17" s="6"/>
+      <x:c r="Q17" s="6"/>
+      <x:c r="R17" s="6"/>
+      <x:c r="S17" s="6"/>
       <x:c r="T17" s="8"/>
       <x:c r="U17" s="8"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="6" t="str">
-        <x:v>manual-16</x:v>
-      </x:c>
-      <x:c r="B18" s="6" t="str">
-        <x:v>Проспект Космонавтов, 92</x:v>
-      </x:c>
-      <x:c r="C18" s="6" t="str"/>
-      <x:c r="D18" s="6" t="n">
-        <x:v>33.6</x:v>
-      </x:c>
-      <x:c r="E18" s="7" t="n">
-        <x:v>46193</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="n">
-        <x:v>11800000</x:v>
-      </x:c>
-      <x:c r="G18" s="8" t="n">
-        <x:v>11600000</x:v>
-      </x:c>
-      <x:c r="H18" s="6" t="str">
-        <x:v>Статус не указан</x:v>
-      </x:c>
+      <x:c r="A18" s="6"/>
+      <x:c r="B18" s="6"/>
+      <x:c r="C18" s="6"/>
+      <x:c r="D18" s="6"/>
+      <x:c r="E18" s="7"/>
+      <x:c r="F18" s="8"/>
+      <x:c r="G18" s="8"/>
+      <x:c r="H18" s="6"/>
       <x:c r="I18" s="7"/>
       <x:c r="J18" s="6"/>
-      <x:c r="K18" s="6" t="str">
-        <x:v>4 из 9</x:v>
-      </x:c>
-      <x:c r="L18" s="6" t="str">
-        <x:v>Кирпичный</x:v>
-      </x:c>
-      <x:c r="M18" s="6" t="n">
-        <x:v>1966</x:v>
-      </x:c>
-      <x:c r="N18" s="6" t="n">
-        <x:v>9.3</x:v>
-      </x:c>
-      <x:c r="O18" s="6" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="P18" s="6" t="str">
-        <x:v>Есть</x:v>
-      </x:c>
-      <x:c r="Q18" s="6" t="str">
-        <x:v>Есть</x:v>
-      </x:c>
-      <x:c r="R18" s="6" t="str">
-        <x:v>Есть</x:v>
-      </x:c>
-      <x:c r="S18" s="6" t="str">
-        <x:v>Звёздная 12 мин пешком</x:v>
-      </x:c>
+      <x:c r="K18" s="6"/>
+      <x:c r="L18" s="6"/>
+      <x:c r="M18" s="6"/>
+      <x:c r="N18" s="6"/>
+      <x:c r="O18" s="6"/>
+      <x:c r="P18" s="6"/>
+      <x:c r="Q18" s="6"/>
+      <x:c r="R18" s="6"/>
+      <x:c r="S18" s="6"/>
       <x:c r="T18" s="8"/>
       <x:c r="U18" s="8"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="6" t="str">
-        <x:v>manual-17</x:v>
-      </x:c>
-      <x:c r="B19" s="6" t="str">
-        <x:v>Адрес не указан (метро Пионерская)</x:v>
-      </x:c>
-      <x:c r="C19" s="6" t="str">
-        <x:v>2-комн. квартира</x:v>
-      </x:c>
-      <x:c r="D19" s="6" t="n">
-        <x:v>50.2</x:v>
-      </x:c>
-      <x:c r="E19" s="7" t="n">
-        <x:v>46212</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="n">
-        <x:v>15990000</x:v>
-      </x:c>
-      <x:c r="G19" s="8" t="n">
-        <x:v>15990000</x:v>
-      </x:c>
-      <x:c r="H19" s="6" t="str">
-        <x:v>Статус не указан</x:v>
-      </x:c>
+      <x:c r="A19" s="6"/>
+      <x:c r="B19" s="6"/>
+      <x:c r="C19" s="6"/>
+      <x:c r="D19" s="6"/>
+      <x:c r="E19" s="7"/>
+      <x:c r="F19" s="8"/>
+      <x:c r="G19" s="8"/>
+      <x:c r="H19" s="6"/>
       <x:c r="I19" s="7"/>
       <x:c r="J19" s="6"/>
-      <x:c r="K19" s="6" t="str">
-        <x:v>8 из 9</x:v>
-      </x:c>
-      <x:c r="L19" s="6" t="str">
-        <x:v>Панельный</x:v>
-      </x:c>
-      <x:c r="M19" s="6" t="n">
-        <x:v>1973</x:v>
-      </x:c>
-      <x:c r="N19" s="6" t="n">
-        <x:v>6.8</x:v>
-      </x:c>
+      <x:c r="K19" s="6"/>
+      <x:c r="L19" s="6"/>
+      <x:c r="M19" s="6"/>
+      <x:c r="N19" s="6"/>
       <x:c r="O19" s="6"/>
-      <x:c r="P19" s="6" t="str"/>
-      <x:c r="Q19" s="6" t="str"/>
-      <x:c r="R19" s="6" t="str"/>
-      <x:c r="S19" s="6" t="str">
-        <x:v>Пионерская 11–15 мин (способ не указан)</x:v>
-      </x:c>
+      <x:c r="P19" s="6"/>
+      <x:c r="Q19" s="6"/>
+      <x:c r="R19" s="6"/>
+      <x:c r="S19" s="6"/>
       <x:c r="T19" s="8"/>
       <x:c r="U19" s="8"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="6" t="str">
-        <x:v>manual-18</x:v>
-      </x:c>
-      <x:c r="B20" s="6" t="str">
-        <x:v>Адрес не указан (метро Звёздная)</x:v>
-      </x:c>
-      <x:c r="C20" s="6" t="str">
-        <x:v>2-комн. квартира</x:v>
-      </x:c>
-      <x:c r="D20" s="6" t="n">
-        <x:v>49.2</x:v>
-      </x:c>
-      <x:c r="E20" s="7" t="n">
-        <x:v>46220</x:v>
-      </x:c>
-      <x:c r="F20" s="8" t="n">
-        <x:v>12990000</x:v>
-      </x:c>
-      <x:c r="G20" s="8" t="n">
-        <x:v>12990000</x:v>
-      </x:c>
-      <x:c r="H20" s="6" t="str">
-        <x:v>Исчезло; продажа не подтверждена</x:v>
-      </x:c>
-      <x:c r="I20" s="7" t="n">
-        <x:v>46231</x:v>
-      </x:c>
+      <x:c r="A20" s="6"/>
+      <x:c r="B20" s="6"/>
+      <x:c r="C20" s="6"/>
+      <x:c r="D20" s="6"/>
+      <x:c r="E20" s="7"/>
+      <x:c r="F20" s="8"/>
+      <x:c r="G20" s="8"/>
+      <x:c r="H20" s="6"/>
+      <x:c r="I20" s="7"/>
       <x:c r="J20" s="6"/>
-      <x:c r="K20" s="6" t="str">
-        <x:v>2 из 5</x:v>
-      </x:c>
-      <x:c r="L20" s="6" t="str">
-        <x:v>Панельный</x:v>
-      </x:c>
-      <x:c r="M20" s="6" t="n">
-        <x:v>1965</x:v>
-      </x:c>
+      <x:c r="K20" s="6"/>
+      <x:c r="L20" s="6"/>
+      <x:c r="M20" s="6"/>
       <x:c r="N20" s="6"/>
       <x:c r="O20" s="6"/>
-      <x:c r="P20" s="6" t="str"/>
-      <x:c r="Q20" s="6" t="str"/>
-      <x:c r="R20" s="6" t="str">
-        <x:v>Нет</x:v>
-      </x:c>
-      <x:c r="S20" s="6" t="str">
-        <x:v>Звёздная</x:v>
-      </x:c>
+      <x:c r="P20" s="6"/>
+      <x:c r="Q20" s="6"/>
+      <x:c r="R20" s="6"/>
+      <x:c r="S20" s="6"/>
       <x:c r="T20" s="8"/>
       <x:c r="U20" s="8"/>
     </x:row>
@@ -2244,7 +2052,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — цены и события со слов пользователя; некоторые даты неизвестны.</x:v>
+        <x:v>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — цены, события и сведения о продаже со слов пользователя.</x:v>
       </x:c>
       <x:c r="B1" s="11"/>
       <x:c r="C1" s="11"/>
@@ -2307,7 +2115,7 @@
         <x:v>Цена из заметок</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Названа ценой продажи</x:v>
+        <x:v>Цена продажи, со слов пользователя</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2364,52 +2172,50 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="6" t="str">
-        <x:v>manual-03</x:v>
+        <x:v>manual-02</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Стародеревенская улица, 6</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="n">
-        <x:v>46095</x:v>
-      </x:c>
-      <x:c r="D8" s="8" t="n">
-        <x:v>12990000</x:v>
-      </x:c>
+        <x:v>Гражданский проспект, 77</x:v>
+      </x:c>
+      <x:c r="C8" s="7"/>
+      <x:c r="D8" s="8"/>
       <x:c r="E8" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F8" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>27.04 объявление исчезло; дата продажи не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="6" t="str">
-        <x:v>manual-03</x:v>
+        <x:v>manual-04</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>Стародеревенская улица, 6</x:v>
-      </x:c>
-      <x:c r="C9" s="7"/>
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="n">
+        <x:v>46076</x:v>
+      </x:c>
       <x:c r="D9" s="8" t="n">
-        <x:v>12800000</x:v>
+        <x:v>22990000</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
         <x:v>Цена из заметок</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="str">
-        <x:v>Дата не указана</x:v>
-      </x:c>
+      <x:c r="F9" s="6" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="6" t="str">
-        <x:v>manual-03</x:v>
+        <x:v>manual-04</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
-        <x:v>Стародеревенская улица, 6</x:v>
+        <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C10" s="7" t="n">
-        <x:v>46206</x:v>
+        <x:v>46118</x:v>
       </x:c>
       <x:c r="D10" s="8" t="n">
-        <x:v>12500000</x:v>
+        <x:v>22500000</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2418,34 +2224,34 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="6" t="str">
-        <x:v>manual-03</x:v>
+        <x:v>manual-04</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>Стародеревенская улица, 6</x:v>
-      </x:c>
-      <x:c r="C11" s="7" t="n">
-        <x:v>46212</x:v>
-      </x:c>
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C11" s="7"/>
       <x:c r="D11" s="8" t="n">
-        <x:v>12300000</x:v>
+        <x:v>23230000</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
         <x:v>Цена из заметок</x:v>
       </x:c>
-      <x:c r="F11" s="6" t="str"/>
+      <x:c r="F11" s="6" t="str">
+        <x:v>Перевыложили, точная дата не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="6" t="str">
-        <x:v>manual-03</x:v>
+        <x:v>manual-04</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>Стародеревенская улица, 6</x:v>
+        <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C12" s="7" t="n">
-        <x:v>46227</x:v>
+        <x:v>46153</x:v>
       </x:c>
       <x:c r="D12" s="8" t="n">
-        <x:v>12500000</x:v>
+        <x:v>23000000</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2460,10 +2266,10 @@
         <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C13" s="7" t="n">
-        <x:v>46076</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="D13" s="8" t="n">
-        <x:v>22990000</x:v>
+        <x:v>22500000</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2478,10 +2284,10 @@
         <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C14" s="7" t="n">
-        <x:v>46118</x:v>
+        <x:v>46174</x:v>
       </x:c>
       <x:c r="D14" s="8" t="n">
-        <x:v>22500000</x:v>
+        <x:v>22000000</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2496,14 +2302,12 @@
         <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C15" s="7"/>
-      <x:c r="D15" s="8" t="n">
-        <x:v>23230000</x:v>
-      </x:c>
+      <x:c r="D15" s="8"/>
       <x:c r="E15" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
+        <x:v>Событие из заметок</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>Перевыложили, точная дата не указана</x:v>
+        <x:v>25.04 исчезло</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2513,16 +2317,14 @@
       <x:c r="B16" s="6" t="str">
         <x:v>Улица Решетникова, 29</x:v>
       </x:c>
-      <x:c r="C16" s="7" t="n">
-        <x:v>46153</x:v>
-      </x:c>
-      <x:c r="D16" s="8" t="n">
-        <x:v>23000000</x:v>
-      </x:c>
+      <x:c r="C16" s="7"/>
+      <x:c r="D16" s="8"/>
       <x:c r="E16" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F16" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>После 25.04 перевыложили за 23 230 000 ₽</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="6" t="str">
@@ -2531,29 +2333,27 @@
       <x:c r="B17" s="6" t="str">
         <x:v>Улица Решетникова, 29</x:v>
       </x:c>
-      <x:c r="C17" s="7" t="n">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="D17" s="8" t="n">
-        <x:v>22500000</x:v>
-      </x:c>
+      <x:c r="C17" s="7"/>
+      <x:c r="D17" s="8"/>
       <x:c r="E17" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F17" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="str">
+        <x:v>25.06 продано — со слов пользователя</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="6" t="str">
-        <x:v>manual-04</x:v>
+        <x:v>manual-05</x:v>
       </x:c>
       <x:c r="B18" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
+        <x:v>Проспект Энгельса, 31</x:v>
       </x:c>
       <x:c r="C18" s="7" t="n">
-        <x:v>46174</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="D18" s="8" t="n">
-        <x:v>22000000</x:v>
+        <x:v>17400000</x:v>
       </x:c>
       <x:c r="E18" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2562,26 +2362,28 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="6" t="str">
-        <x:v>manual-04</x:v>
+        <x:v>manual-05</x:v>
       </x:c>
       <x:c r="B19" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
-      </x:c>
-      <x:c r="C19" s="7"/>
-      <x:c r="D19" s="8"/>
+        <x:v>Проспект Энгельса, 31</x:v>
+      </x:c>
+      <x:c r="C19" s="7" t="n">
+        <x:v>46132</x:v>
+      </x:c>
+      <x:c r="D19" s="8" t="n">
+        <x:v>16990000</x:v>
+      </x:c>
       <x:c r="E19" s="6" t="str">
-        <x:v>Событие из заметок</x:v>
-      </x:c>
-      <x:c r="F19" s="6" t="str">
-        <x:v>25.04 исчезло</x:v>
-      </x:c>
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F19" s="6" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="6" t="str">
-        <x:v>manual-04</x:v>
+        <x:v>manual-05</x:v>
       </x:c>
       <x:c r="B20" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
+        <x:v>Проспект Энгельса, 31</x:v>
       </x:c>
       <x:c r="C20" s="7"/>
       <x:c r="D20" s="8"/>
@@ -2589,55 +2391,57 @@
         <x:v>Событие из заметок</x:v>
       </x:c>
       <x:c r="F20" s="6" t="str">
-        <x:v>После 25.04 перевыложили за 23 230 000 ₽</x:v>
+        <x:v>08.06 объявление исчезло; дата продажи не указана</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="6" t="str">
-        <x:v>manual-04</x:v>
+        <x:v>manual-07</x:v>
       </x:c>
       <x:c r="B21" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
-      </x:c>
-      <x:c r="C21" s="7"/>
-      <x:c r="D21" s="8"/>
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="n">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="D21" s="8" t="n">
+        <x:v>23900000</x:v>
+      </x:c>
       <x:c r="E21" s="6" t="str">
-        <x:v>Событие из заметок</x:v>
-      </x:c>
-      <x:c r="F21" s="6" t="str">
-        <x:v>25.06 продано — со слов пользователя</x:v>
-      </x:c>
+        <x:v>Цена из заметок</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="6" t="str">
-        <x:v>manual-05</x:v>
+        <x:v>manual-07</x:v>
       </x:c>
       <x:c r="B22" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
-      </x:c>
-      <x:c r="C22" s="7" t="n">
-        <x:v>46107</x:v>
-      </x:c>
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C22" s="7"/>
       <x:c r="D22" s="8" t="n">
-        <x:v>17400000</x:v>
+        <x:v>23500000</x:v>
       </x:c>
       <x:c r="E22" s="6" t="str">
         <x:v>Цена из заметок</x:v>
       </x:c>
-      <x:c r="F22" s="6" t="str"/>
+      <x:c r="F22" s="6" t="str">
+        <x:v>Дата не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="6" t="str">
-        <x:v>manual-05</x:v>
+        <x:v>manual-07</x:v>
       </x:c>
       <x:c r="B23" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
+        <x:v>Улица Стахановцев, 1</x:v>
       </x:c>
       <x:c r="C23" s="7" t="n">
-        <x:v>46132</x:v>
+        <x:v>46193</x:v>
       </x:c>
       <x:c r="D23" s="8" t="n">
-        <x:v>16990000</x:v>
+        <x:v>23000000</x:v>
       </x:c>
       <x:c r="E23" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2646,34 +2450,32 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="6" t="str">
-        <x:v>manual-06</x:v>
+        <x:v>manual-07</x:v>
       </x:c>
       <x:c r="B24" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
-      </x:c>
-      <x:c r="C24" s="7" t="n">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="D24" s="8" t="n">
-        <x:v>14990000</x:v>
-      </x:c>
+        <x:v>Улица Стахановцев, 1</x:v>
+      </x:c>
+      <x:c r="C24" s="7"/>
+      <x:c r="D24" s="8"/>
       <x:c r="E24" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F24" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>24.07 объявление исчезло; дата продажи не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="6" t="str">
-        <x:v>manual-06</x:v>
+        <x:v>manual-09</x:v>
       </x:c>
       <x:c r="B25" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
+        <x:v>Улица Орджоникидзе, 6</x:v>
       </x:c>
       <x:c r="C25" s="7" t="n">
-        <x:v>46132</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="D25" s="8" t="n">
-        <x:v>14800000</x:v>
+        <x:v>10990000</x:v>
       </x:c>
       <x:c r="E25" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2682,16 +2484,16 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="6" t="str">
-        <x:v>manual-06</x:v>
+        <x:v>manual-09</x:v>
       </x:c>
       <x:c r="B26" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
+        <x:v>Улица Орджоникидзе, 6</x:v>
       </x:c>
       <x:c r="C26" s="7" t="n">
-        <x:v>46190</x:v>
+        <x:v>46168</x:v>
       </x:c>
       <x:c r="D26" s="8" t="n">
-        <x:v>14600000</x:v>
+        <x:v>10800000</x:v>
       </x:c>
       <x:c r="E26" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2700,34 +2502,32 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="6" t="str">
-        <x:v>manual-06</x:v>
+        <x:v>manual-09</x:v>
       </x:c>
       <x:c r="B27" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
-      </x:c>
-      <x:c r="C27" s="7" t="n">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="D27" s="8" t="n">
-        <x:v>14300000</x:v>
-      </x:c>
+        <x:v>Улица Орджоникидзе, 6</x:v>
+      </x:c>
+      <x:c r="C27" s="7"/>
+      <x:c r="D27" s="8"/>
       <x:c r="E27" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F27" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>23.06 объявление исчезло; дата продажи не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="6" t="str">
-        <x:v>manual-06</x:v>
+        <x:v>manual-10</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
-        <x:v>Проспект Энгельса, 31</x:v>
+        <x:v>Улица Орджоникидзе, 39</x:v>
       </x:c>
       <x:c r="C28" s="7" t="n">
-        <x:v>46231</x:v>
+        <x:v>46142</x:v>
       </x:c>
       <x:c r="D28" s="8" t="n">
-        <x:v>14100000</x:v>
+        <x:v>12990000</x:v>
       </x:c>
       <x:c r="E28" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2736,52 +2536,50 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="6" t="str">
-        <x:v>manual-07</x:v>
+        <x:v>manual-10</x:v>
       </x:c>
       <x:c r="B29" s="6" t="str">
-        <x:v>Улица Стахановцев, 1</x:v>
-      </x:c>
-      <x:c r="C29" s="7" t="n">
-        <x:v>46112</x:v>
-      </x:c>
+        <x:v>Улица Орджоникидзе, 39</x:v>
+      </x:c>
+      <x:c r="C29" s="7"/>
       <x:c r="D29" s="8" t="n">
-        <x:v>23900000</x:v>
+        <x:v>12800000</x:v>
       </x:c>
       <x:c r="E29" s="6" t="str">
         <x:v>Цена из заметок</x:v>
       </x:c>
-      <x:c r="F29" s="6" t="str"/>
+      <x:c r="F29" s="6" t="str">
+        <x:v>Дата не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="6" t="str">
-        <x:v>manual-07</x:v>
+        <x:v>manual-10</x:v>
       </x:c>
       <x:c r="B30" s="6" t="str">
-        <x:v>Улица Стахановцев, 1</x:v>
+        <x:v>Улица Орджоникидзе, 39</x:v>
       </x:c>
       <x:c r="C30" s="7"/>
-      <x:c r="D30" s="8" t="n">
-        <x:v>23500000</x:v>
-      </x:c>
+      <x:c r="D30" s="8"/>
       <x:c r="E30" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
+        <x:v>Событие из заметок</x:v>
       </x:c>
       <x:c r="F30" s="6" t="str">
-        <x:v>Дата не указана</x:v>
+        <x:v>23.05 объявление исчезло; дата продажи не указана</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="6" t="str">
-        <x:v>manual-07</x:v>
+        <x:v>manual-13</x:v>
       </x:c>
       <x:c r="B31" s="6" t="str">
-        <x:v>Улица Стахановцев, 1</x:v>
+        <x:v>Проспект Науки, 14к1</x:v>
       </x:c>
       <x:c r="C31" s="7" t="n">
-        <x:v>46193</x:v>
+        <x:v>46179</x:v>
       </x:c>
       <x:c r="D31" s="8" t="n">
-        <x:v>23000000</x:v>
+        <x:v>10500000</x:v>
       </x:c>
       <x:c r="E31" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2790,70 +2588,64 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="6" t="str">
-        <x:v>manual-08</x:v>
+        <x:v>manual-13</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
-        <x:v>Улица Маршала Новикова, 9</x:v>
-      </x:c>
-      <x:c r="C32" s="7" t="n">
-        <x:v>46121</x:v>
-      </x:c>
-      <x:c r="D32" s="8" t="n">
-        <x:v>12500000</x:v>
-      </x:c>
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C32" s="7"/>
+      <x:c r="D32" s="8"/>
       <x:c r="E32" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F32" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>06.07 продано — со слов пользователя</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="6" t="str">
-        <x:v>manual-08</x:v>
+        <x:v>manual-13</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
-        <x:v>Улица Маршала Новикова, 9</x:v>
-      </x:c>
-      <x:c r="C33" s="7" t="n">
-        <x:v>46214</x:v>
-      </x:c>
-      <x:c r="D33" s="8" t="n">
-        <x:v>12300000</x:v>
-      </x:c>
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C33" s="7"/>
+      <x:c r="D33" s="8"/>
       <x:c r="E33" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F33" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>Затем вновь появилось, дата не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="6" t="str">
-        <x:v>manual-09</x:v>
+        <x:v>manual-13</x:v>
       </x:c>
       <x:c r="B34" s="6" t="str">
-        <x:v>Улица Орджоникидзе, 6</x:v>
-      </x:c>
-      <x:c r="C34" s="7" t="n">
-        <x:v>46138</x:v>
-      </x:c>
-      <x:c r="D34" s="8" t="n">
-        <x:v>10990000</x:v>
-      </x:c>
+        <x:v>Проспект Науки, 14к1</x:v>
+      </x:c>
+      <x:c r="C34" s="7"/>
+      <x:c r="D34" s="8"/>
       <x:c r="E34" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F34" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="str">
+        <x:v>15.07 вновь исчезло</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="6" t="str">
-        <x:v>manual-09</x:v>
+        <x:v>manual-14</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
-        <x:v>Улица Орджоникидзе, 6</x:v>
+        <x:v>Проспект Тореза, 102</x:v>
       </x:c>
       <x:c r="C35" s="7" t="n">
-        <x:v>46168</x:v>
+        <x:v>46184</x:v>
       </x:c>
       <x:c r="D35" s="8" t="n">
-        <x:v>10800000</x:v>
+        <x:v>15000000</x:v>
       </x:c>
       <x:c r="E35" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2862,52 +2654,50 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="6" t="str">
-        <x:v>manual-10</x:v>
+        <x:v>manual-14</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
-        <x:v>Улица Орджоникидзе, 39</x:v>
-      </x:c>
-      <x:c r="C36" s="7" t="n">
-        <x:v>46142</x:v>
-      </x:c>
-      <x:c r="D36" s="8" t="n">
-        <x:v>12990000</x:v>
-      </x:c>
+        <x:v>Проспект Тореза, 102</x:v>
+      </x:c>
+      <x:c r="C36" s="7"/>
+      <x:c r="D36" s="8"/>
       <x:c r="E36" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F36" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>23.06 объявление закрылось; дата продажи не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="6" t="str">
-        <x:v>manual-10</x:v>
+        <x:v>manual-15</x:v>
       </x:c>
       <x:c r="B37" s="6" t="str">
-        <x:v>Улица Орджоникидзе, 39</x:v>
-      </x:c>
-      <x:c r="C37" s="7"/>
+        <x:v>Улица Решетникова, 29</x:v>
+      </x:c>
+      <x:c r="C37" s="7" t="n">
+        <x:v>46187</x:v>
+      </x:c>
       <x:c r="D37" s="8" t="n">
-        <x:v>12800000</x:v>
+        <x:v>29000000</x:v>
       </x:c>
       <x:c r="E37" s="6" t="str">
         <x:v>Цена из заметок</x:v>
       </x:c>
-      <x:c r="F37" s="6" t="str">
-        <x:v>Дата не указана</x:v>
-      </x:c>
+      <x:c r="F37" s="6" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="6" t="str">
-        <x:v>manual-11</x:v>
+        <x:v>manual-15</x:v>
       </x:c>
       <x:c r="B38" s="6" t="str">
-        <x:v>Коломяжский проспект, 13к2</x:v>
+        <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C38" s="7" t="n">
-        <x:v>46163</x:v>
+        <x:v>46206</x:v>
       </x:c>
       <x:c r="D38" s="8" t="n">
-        <x:v>20500000</x:v>
+        <x:v>28500000</x:v>
       </x:c>
       <x:c r="E38" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2916,34 +2706,36 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="6" t="str">
-        <x:v>manual-11</x:v>
+        <x:v>manual-15</x:v>
       </x:c>
       <x:c r="B39" s="6" t="str">
-        <x:v>Коломяжский проспект, 13к2</x:v>
+        <x:v>Улица Решетникова, 29</x:v>
       </x:c>
       <x:c r="C39" s="7" t="n">
-        <x:v>46224</x:v>
+        <x:v>46308</x:v>
       </x:c>
       <x:c r="D39" s="8" t="n">
-        <x:v>19990000</x:v>
+        <x:v>28000000</x:v>
       </x:c>
       <x:c r="E39" s="6" t="str">
         <x:v>Цена из заметок</x:v>
       </x:c>
-      <x:c r="F39" s="6" t="str"/>
+      <x:c r="F39" s="6" t="str">
+        <x:v>Цена продажи, со слов пользователя</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="6" t="str">
-        <x:v>manual-12</x:v>
+        <x:v>manual-18</x:v>
       </x:c>
       <x:c r="B40" s="6" t="str">
-        <x:v>Бухарестская улица, 86</x:v>
+        <x:v>Адрес не указан (метро Звёздная)</x:v>
       </x:c>
       <x:c r="C40" s="7" t="n">
-        <x:v>46166</x:v>
+        <x:v>46220</x:v>
       </x:c>
       <x:c r="D40" s="8" t="n">
-        <x:v>14000000</x:v>
+        <x:v>12990000</x:v>
       </x:c>
       <x:c r="E40" s="6" t="str">
         <x:v>Цена из заметок</x:v>
@@ -2952,213 +2744,107 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="6" t="str">
-        <x:v>manual-12</x:v>
+        <x:v>manual-18</x:v>
       </x:c>
       <x:c r="B41" s="6" t="str">
-        <x:v>Бухарестская улица, 86</x:v>
-      </x:c>
-      <x:c r="C41" s="7" t="n">
-        <x:v>46217</x:v>
-      </x:c>
-      <x:c r="D41" s="8" t="n">
-        <x:v>13800000</x:v>
-      </x:c>
+        <x:v>Адрес не указан (метро Звёздная)</x:v>
+      </x:c>
+      <x:c r="C41" s="7"/>
+      <x:c r="D41" s="8"/>
       <x:c r="E41" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F41" s="6" t="str"/>
+        <x:v>Событие из заметок</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>28.07 объявление исчезло; дата продажи не указана</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="6" t="str">
-        <x:v>manual-13</x:v>
-      </x:c>
-      <x:c r="B42" s="6" t="str">
-        <x:v>Проспект Науки, 14к1</x:v>
-      </x:c>
-      <x:c r="C42" s="7" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="D42" s="8" t="n">
-        <x:v>10500000</x:v>
-      </x:c>
-      <x:c r="E42" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F42" s="6" t="str"/>
+      <x:c r="A42" s="6"/>
+      <x:c r="B42" s="6"/>
+      <x:c r="C42" s="7"/>
+      <x:c r="D42" s="8"/>
+      <x:c r="E42" s="6"/>
+      <x:c r="F42" s="6"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="6" t="str">
-        <x:v>manual-13</x:v>
-      </x:c>
-      <x:c r="B43" s="6" t="str">
-        <x:v>Проспект Науки, 14к1</x:v>
-      </x:c>
+      <x:c r="A43" s="6"/>
+      <x:c r="B43" s="6"/>
       <x:c r="C43" s="7"/>
       <x:c r="D43" s="8"/>
-      <x:c r="E43" s="6" t="str">
-        <x:v>Событие из заметок</x:v>
-      </x:c>
-      <x:c r="F43" s="6" t="str">
-        <x:v>06.07 продано — со слов пользователя</x:v>
-      </x:c>
+      <x:c r="E43" s="6"/>
+      <x:c r="F43" s="6"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="6" t="str">
-        <x:v>manual-13</x:v>
-      </x:c>
-      <x:c r="B44" s="6" t="str">
-        <x:v>Проспект Науки, 14к1</x:v>
-      </x:c>
+      <x:c r="A44" s="6"/>
+      <x:c r="B44" s="6"/>
       <x:c r="C44" s="7"/>
       <x:c r="D44" s="8"/>
-      <x:c r="E44" s="6" t="str">
-        <x:v>Событие из заметок</x:v>
-      </x:c>
-      <x:c r="F44" s="6" t="str">
-        <x:v>Затем вновь появилось, дата не указана</x:v>
-      </x:c>
+      <x:c r="E44" s="6"/>
+      <x:c r="F44" s="6"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="6" t="str">
-        <x:v>manual-13</x:v>
-      </x:c>
-      <x:c r="B45" s="6" t="str">
-        <x:v>Проспект Науки, 14к1</x:v>
-      </x:c>
+      <x:c r="A45" s="6"/>
+      <x:c r="B45" s="6"/>
       <x:c r="C45" s="7"/>
       <x:c r="D45" s="8"/>
-      <x:c r="E45" s="6" t="str">
-        <x:v>Событие из заметок</x:v>
-      </x:c>
-      <x:c r="F45" s="6" t="str">
-        <x:v>15.07 вновь исчезло</x:v>
-      </x:c>
+      <x:c r="E45" s="6"/>
+      <x:c r="F45" s="6"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="6" t="str">
-        <x:v>manual-14</x:v>
-      </x:c>
-      <x:c r="B46" s="6" t="str">
-        <x:v>Проспект Тореза, 102</x:v>
-      </x:c>
-      <x:c r="C46" s="7" t="n">
-        <x:v>46184</x:v>
-      </x:c>
-      <x:c r="D46" s="8" t="n">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="E46" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F46" s="6" t="str"/>
+      <x:c r="A46" s="6"/>
+      <x:c r="B46" s="6"/>
+      <x:c r="C46" s="7"/>
+      <x:c r="D46" s="8"/>
+      <x:c r="E46" s="6"/>
+      <x:c r="F46" s="6"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="6" t="str">
-        <x:v>manual-15</x:v>
-      </x:c>
-      <x:c r="B47" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
-      </x:c>
-      <x:c r="C47" s="7" t="n">
-        <x:v>46187</x:v>
-      </x:c>
-      <x:c r="D47" s="8" t="n">
-        <x:v>29000000</x:v>
-      </x:c>
-      <x:c r="E47" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F47" s="6" t="str"/>
+      <x:c r="A47" s="6"/>
+      <x:c r="B47" s="6"/>
+      <x:c r="C47" s="7"/>
+      <x:c r="D47" s="8"/>
+      <x:c r="E47" s="6"/>
+      <x:c r="F47" s="6"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="6" t="str">
-        <x:v>manual-15</x:v>
-      </x:c>
-      <x:c r="B48" s="6" t="str">
-        <x:v>Улица Решетникова, 29</x:v>
-      </x:c>
-      <x:c r="C48" s="7" t="n">
-        <x:v>46206</x:v>
-      </x:c>
-      <x:c r="D48" s="8" t="n">
-        <x:v>28500000</x:v>
-      </x:c>
-      <x:c r="E48" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F48" s="6" t="str"/>
+      <x:c r="A48" s="6"/>
+      <x:c r="B48" s="6"/>
+      <x:c r="C48" s="7"/>
+      <x:c r="D48" s="8"/>
+      <x:c r="E48" s="6"/>
+      <x:c r="F48" s="6"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="6" t="str">
-        <x:v>manual-16</x:v>
-      </x:c>
-      <x:c r="B49" s="6" t="str">
-        <x:v>Проспект Космонавтов, 92</x:v>
-      </x:c>
-      <x:c r="C49" s="7" t="n">
-        <x:v>46193</x:v>
-      </x:c>
-      <x:c r="D49" s="8" t="n">
-        <x:v>11800000</x:v>
-      </x:c>
-      <x:c r="E49" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F49" s="6" t="str"/>
+      <x:c r="A49" s="6"/>
+      <x:c r="B49" s="6"/>
+      <x:c r="C49" s="7"/>
+      <x:c r="D49" s="8"/>
+      <x:c r="E49" s="6"/>
+      <x:c r="F49" s="6"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="6" t="str">
-        <x:v>manual-16</x:v>
-      </x:c>
-      <x:c r="B50" s="6" t="str">
-        <x:v>Проспект Космонавтов, 92</x:v>
-      </x:c>
-      <x:c r="C50" s="7" t="n">
-        <x:v>46213</x:v>
-      </x:c>
-      <x:c r="D50" s="8" t="n">
-        <x:v>11600000</x:v>
-      </x:c>
-      <x:c r="E50" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F50" s="6" t="str"/>
+      <x:c r="A50" s="6"/>
+      <x:c r="B50" s="6"/>
+      <x:c r="C50" s="7"/>
+      <x:c r="D50" s="8"/>
+      <x:c r="E50" s="6"/>
+      <x:c r="F50" s="6"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="6" t="str">
-        <x:v>manual-17</x:v>
-      </x:c>
-      <x:c r="B51" s="6" t="str">
-        <x:v>Адрес не указан (метро Пионерская)</x:v>
-      </x:c>
-      <x:c r="C51" s="7" t="n">
-        <x:v>46212</x:v>
-      </x:c>
-      <x:c r="D51" s="8" t="n">
-        <x:v>15990000</x:v>
-      </x:c>
-      <x:c r="E51" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F51" s="6" t="str"/>
+      <x:c r="A51" s="6"/>
+      <x:c r="B51" s="6"/>
+      <x:c r="C51" s="7"/>
+      <x:c r="D51" s="8"/>
+      <x:c r="E51" s="6"/>
+      <x:c r="F51" s="6"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="6" t="str">
-        <x:v>manual-18</x:v>
-      </x:c>
-      <x:c r="B52" s="6" t="str">
-        <x:v>Адрес не указан (метро Звёздная)</x:v>
-      </x:c>
-      <x:c r="C52" s="7" t="n">
-        <x:v>46220</x:v>
-      </x:c>
-      <x:c r="D52" s="8" t="n">
-        <x:v>12990000</x:v>
-      </x:c>
-      <x:c r="E52" s="6" t="str">
-        <x:v>Цена из заметок</x:v>
-      </x:c>
-      <x:c r="F52" s="6" t="str"/>
+      <x:c r="A52" s="6"/>
+      <x:c r="B52" s="6"/>
+      <x:c r="C52" s="7"/>
+      <x:c r="D52" s="8"/>
+      <x:c r="E52" s="6"/>
+      <x:c r="F52" s="6"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="R33050958525f4235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История цен" sheetId="2" r:id="R1ada1ce07b914ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Старый архив" sheetId="3" r:id="Ra9eedd37419c4984"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены старого архива" sheetId="4" r:id="Rb21b1a79c38c474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Объявления" sheetId="1" r:id="R12e6dd633c774100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История цен" sheetId="2" r:id="Ra7c4d93cf467425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Старый архив" sheetId="3" r:id="R0e1525eee32642f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Цены старого архива" sheetId="4" r:id="Rbd480a16f1ee41ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1514,13 +1514,13 @@
         <x:v>22990000</x:v>
       </x:c>
       <x:c r="G5" s="8" t="n">
-        <x:v>22000000</x:v>
+        <x:v>21000000</x:v>
       </x:c>
       <x:c r="H5" s="6" t="str">
-        <x:v>Продано 25.06 — со слов пользователя</x:v>
+        <x:v>Продано — со слов пользователя</x:v>
       </x:c>
       <x:c r="I5" s="7" t="n">
-        <x:v>46198</x:v>
+        <x:v>46266</x:v>
       </x:c>
       <x:c r="J5" s="6"/>
       <x:c r="K5" s="6" t="str"/>
@@ -2333,13 +2333,17 @@
       <x:c r="B17" s="6" t="str">
         <x:v>Улица Решетникова, 29</x:v>
       </x:c>
-      <x:c r="C17" s="7"/>
-      <x:c r="D17" s="8"/>
+      <x:c r="C17" s="7" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="D17" s="8" t="n">
+        <x:v>21000000</x:v>
+      </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>Событие из заметок</x:v>
+        <x:v>Цена из заметок</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>25.06 продано — со слов пользователя</x:v>
+        <x:v>Цена продажи, со слов пользователя</x:v>
       </x:c>
     </x:row>
     <x:row r="18">

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -12,8 +12,8 @@
     <x:sheet name="Цены старого архива" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$X$6</x:definedName>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$8</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$X$7</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$9</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Старый архив'!$A$2:$U$13</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Цены старого архива'!$A$2:$F$41</x:definedName>
   </x:definedNames>
@@ -96,15 +96,51 @@
     <x:t>Ссылка</x:t>
   </x:si>
   <x:si>
+    <x:t>335053290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Московский, Московская застава, м. Электросила, улица Решетникова, 29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Московский, Московская застава, м. Электросила, улица Решетникова, 29</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>4 из 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>monolithBrick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Электросила</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>В профиле</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-18T15:15:29.2091171+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-17T12:42:27.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
+  </x:si>
+  <x:si>
     <x:t>334110300</x:t>
   </x:si>
   <x:si>
     <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
   </x:si>
   <x:si>
-    <x:t>2-комн. квартира</x:t>
-  </x:si>
-  <x:si>
     <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
   </x:si>
   <x:si>
@@ -126,138 +162,135 @@
     <x:t>18 мин пешком</x:t>
   </x:si>
   <x:si>
-    <x:t>В профиле</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-17T19:12:01.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334909733</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Академическая</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-17T19:11:42.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>330348790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Проспект Славы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-17T19:11:55.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332861239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 из 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Комендантский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-17T19:11:35.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334653328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 лоджия</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 из 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Кирпичный</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Парк Победы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7 мин на транспорте</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Нет в профиле</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-16T15:20:38.3153475+00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-12T09:46:25.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334909733</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>6 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Академическая</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-15T11:59:03.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>330348790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Проспект Славы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T19:26:32.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>332861239</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10 из 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Комендантский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-16T17:00:50.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334653328</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 лоджия</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 из 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Кирпичный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Парк Победы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7 мин на транспорте</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-10-12T09:46:40.0000000+03:00</x:t>
   </x:si>
   <x:si>
@@ -328,9 +361,6 @@
   </x:si>
   <x:si>
     <x:t>Улица Решетникова, 29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Электросила</x:t>
   </x:si>
   <x:si>
     <x:t>manual-05</x:t>
@@ -865,7 +895,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:X6"/>
+  <x:dimension ref="A1:X7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18.710625" style="0" customWidth="1"/>
@@ -964,10 +994,10 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>50.6</x:v>
+        <x:v>49.6</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>5.8</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>28</x:v>
@@ -976,78 +1006,72 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="0">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J2" s="0">
-        <x:v>1970</x:v>
+        <x:v>2023</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="M2" s="0">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="N2" s="0" t="s">
+      <x:c r="O2" s="0" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="O2" s="0" t="s">
+      <x:c r="P2" s="0">
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>15000000</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
+      <x:c r="S2" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S2" s="0" t="s">
+      <x:c r="U2" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="W2" s="0" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="T2" s="0" t="s">
+      <x:c r="X2" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="U2" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="V2" s="0">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="W2" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="X2" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:24">
       <x:c r="A3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>44.6</x:v>
+        <x:v>50.6</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>7.8</x:v>
+        <x:v>5.8</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>9</x:v>
@@ -1056,7 +1080,7 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>43</x:v>
@@ -1065,31 +1089,31 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="O3" s="0" t="s">
+      <x:c r="P3" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>15000000</x:v>
+      </x:c>
+      <x:c r="R3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S3" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="P3" s="0">
-        <x:v>14000000</x:v>
-      </x:c>
-      <x:c r="Q3" s="0">
-        <x:v>14000000</x:v>
-      </x:c>
-      <x:c r="R3" s="0" t="s">
+      <x:c r="T3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="U3" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S3" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="T3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="U3" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="V3" s="0">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
         <x:v>48</x:v>
@@ -1112,13 +1136,13 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>44.3</x:v>
+        <x:v>44.6</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>7</x:v>
+        <x:v>7.8</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>53</x:v>
@@ -1127,16 +1151,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="J4" s="0">
-        <x:v>1967</x:v>
+        <x:v>1970</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M4" s="0">
-        <x:v>2.55</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>54</x:v>
@@ -1145,25 +1169,25 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>13300000</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>13200000</x:v>
+        <x:v>14000000</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>146</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
         <x:v>57</x:v>
@@ -1180,148 +1204,222 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="E5" s="0">
+        <x:v>44.3</x:v>
+      </x:c>
+      <x:c r="F5" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E5" s="0">
-        <x:v>38.7</x:v>
-      </x:c>
-      <x:c r="F5" s="0">
-        <x:v>10.1</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="I5" s="0">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J5" s="0">
-        <x:v>1986</x:v>
+        <x:v>1967</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="M5" s="0">
-        <x:v>2.65</x:v>
+        <x:v>2.55</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="O5" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="O5" s="0" t="s">
+      <x:c r="P5" s="0">
+        <x:v>13300000</x:v>
+      </x:c>
+      <x:c r="Q5" s="0">
+        <x:v>13200000</x:v>
+      </x:c>
+      <x:c r="R5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S5" s="0" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="P5" s="0">
-        <x:v>12990000</x:v>
-      </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>12800000</x:v>
-      </x:c>
-      <x:c r="R5" s="0" t="s">
+      <x:c r="T5" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="U5" s="0" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="S5" s="0" t="s">
+      <x:c r="V5" s="0">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="W5" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="T5" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="U5" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="V5" s="0">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="W5" s="0" t="s">
+      <x:c r="X5" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="X5" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:24">
       <x:c r="A6" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="C6" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="E6" s="0">
+        <x:v>38.7</x:v>
+      </x:c>
+      <x:c r="F6" s="0">
+        <x:v>10.1</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I6" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J6" s="0">
+        <x:v>1986</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M6" s="0">
+        <x:v>2.65</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="O6" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="P6" s="0">
+        <x:v>12990000</x:v>
+      </x:c>
+      <x:c r="Q6" s="0">
+        <x:v>12800000</x:v>
+      </x:c>
+      <x:c r="R6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="S6" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="T6" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="U6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="V6" s="0">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="W6" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="X6" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:24">
+      <x:c r="A7" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E7" s="0">
         <x:v>36.8</x:v>
       </x:c>
-      <x:c r="F6" s="0">
+      <x:c r="F7" s="0">
         <x:v>7.8</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="I6" s="0">
+      <x:c r="G7" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I7" s="0">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="J6" s="0">
+      <x:c r="J7" s="0">
         <x:v>1970</x:v>
       </x:c>
-      <x:c r="K6" s="0" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="M6" s="0">
+      <x:c r="K7" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M7" s="0">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="N6" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="O6" s="0" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="P6" s="0">
+      <x:c r="N7" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="O7" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="P7" s="0">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="Q6" s="0">
+      <x:c r="Q7" s="0">
         <x:v>13000000</x:v>
       </x:c>
-      <x:c r="R6" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="S6" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="T6" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="U6" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="V6" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="W6" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="X6" s="0" t="s">
-        <x:v>79</x:v>
+      <x:c r="R7" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="S7" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="T7" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="U7" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="V7" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="W7" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="X7" s="0" t="s">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:X6"/>
+  <x:autoFilter ref="A1:X7"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -1335,7 +1433,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E8"/>
+  <x:dimension ref="A1:E9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="19.710625" style="0" customWidth="1"/>
@@ -1352,10 +1450,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>23</x:v>
@@ -1363,125 +1461,142 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D2" s="0">
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>14000000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D4" s="0">
         <x:v>13300000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>13200000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D9" s="0">
+        <x:v>28000000</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:E8"/>
+  <x:autoFilter ref="A1:E9"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -1509,12 +1624,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:21">
       <x:c r="A1" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:21" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
@@ -1526,22 +1641,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
         <x:v>7</x:v>
@@ -1559,33 +1674,33 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P2" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="S2" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="T2" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="U2" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:21">
       <x:c r="A3" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>31</x:v>
@@ -1600,7 +1715,7 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I3" s="4">
         <x:v>46119</x:v>
@@ -1609,22 +1724,22 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="T3" s="0">
         <x:v>5950000</x:v>
@@ -1635,13 +1750,13 @@
     </x:row>
     <x:row r="4" spans="1:21">
       <x:c r="A4" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="0">
         <x:v>35</x:v>
@@ -1656,39 +1771,39 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:21">
       <x:c r="A5" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>45</x:v>
@@ -1703,39 +1818,39 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I5" s="4">
         <x:v>46266</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:21">
       <x:c r="A6" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>37.8</x:v>
@@ -1750,36 +1865,36 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:21">
       <x:c r="A7" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>41</x:v>
@@ -1794,13 +1909,13 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M7" s="0">
         <x:v>2024</x:v>
@@ -1809,27 +1924,27 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="P7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:21">
       <x:c r="A8" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>30</x:v>
@@ -1844,36 +1959,36 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:21">
       <x:c r="A9" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="0">
         <x:v>37</x:v>
@@ -1888,39 +2003,39 @@
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:21">
       <x:c r="A10" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="0">
         <x:v>30.6</x:v>
@@ -1935,36 +2050,36 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:21">
       <x:c r="A11" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>51.5</x:v>
@@ -1979,36 +2094,36 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R11" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:21">
       <x:c r="A12" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D12" s="0">
         <x:v>54</x:v>
@@ -2023,36 +2138,36 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I12" s="4">
         <x:v>46308</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:21">
       <x:c r="A13" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>26</x:v>
@@ -2070,28 +2185,28 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="M13" s="0">
         <x:v>1965</x:v>
       </x:c>
       <x:c r="P13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2123,35 +2238,35 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C3" s="4">
         <x:v>46048</x:v>
@@ -2160,18 +2275,18 @@
         <x:v>9990000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C4" s="4">
         <x:v>46119</x:v>
@@ -2180,18 +2295,18 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C5" s="4">
         <x:v>46067</x:v>
@@ -2200,18 +2315,18 @@
         <x:v>11700000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C6" s="4">
         <x:v>46129</x:v>
@@ -2220,46 +2335,46 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
       <x:c r="A9" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C9" s="4">
         <x:v>46076</x:v>
@@ -2268,18 +2383,18 @@
         <x:v>22990000</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C10" s="4">
         <x:v>46118</x:v>
@@ -2288,35 +2403,35 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>23230000</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C12" s="4">
         <x:v>46153</x:v>
@@ -2325,18 +2440,18 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C13" s="4">
         <x:v>46162</x:v>
@@ -2345,18 +2460,18 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6">
       <x:c r="A14" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C14" s="4">
         <x:v>46174</x:v>
@@ -2365,18 +2480,18 @@
         <x:v>22000000</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C15" s="4">
         <x:v>46266</x:v>
@@ -2385,46 +2500,46 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C18" s="4">
         <x:v>46107</x:v>
@@ -2433,18 +2548,18 @@
         <x:v>17400000</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C19" s="4">
         <x:v>46132</x:v>
@@ -2453,32 +2568,32 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C21" s="4">
         <x:v>46112</x:v>
@@ -2487,35 +2602,35 @@
         <x:v>23900000</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>23500000</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C23" s="4">
         <x:v>46193</x:v>
@@ -2524,32 +2639,32 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C25" s="4">
         <x:v>46138</x:v>
@@ -2558,18 +2673,18 @@
         <x:v>10990000</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C26" s="4">
         <x:v>46168</x:v>
@@ -2578,32 +2693,32 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:6">
       <x:c r="A27" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C28" s="4">
         <x:v>46142</x:v>
@@ -2612,49 +2727,49 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C31" s="4">
         <x:v>46179</x:v>
@@ -2663,60 +2778,60 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C35" s="4">
         <x:v>46184</x:v>
@@ -2725,32 +2840,32 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C37" s="4">
         <x:v>46187</x:v>
@@ -2759,18 +2874,18 @@
         <x:v>29000000</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C38" s="4">
         <x:v>46206</x:v>
@@ -2779,18 +2894,18 @@
         <x:v>28500000</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C39" s="4">
         <x:v>46308</x:v>
@@ -2799,18 +2914,18 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C40" s="4">
         <x:v>46220</x:v>
@@ -2819,24 +2934,24 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -129,7 +129,10 @@
     <x:t>2026-10-18T15:15:29.2091171+00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-17T12:42:27.0000000+03:00</x:t>
+    <x:t>2026-10-20T15:24:02.1835444+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-19T21:30:06.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
@@ -168,7 +171,7 @@
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-17T19:12:01.0000000+03:00</x:t>
+    <x:t>2026-10-19T21:30:24.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
@@ -195,7 +198,7 @@
     <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-17T19:11:42.0000000+03:00</x:t>
+    <x:t>2026-10-19T21:30:16.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
@@ -222,7 +225,7 @@
     <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-17T19:11:55.0000000+03:00</x:t>
+    <x:t>2026-10-19T21:30:20.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
@@ -252,7 +255,7 @@
     <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-17T19:11:35.0000000+03:00</x:t>
+    <x:t>2026-10-19T21:30:11.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
@@ -1039,27 +1042,27 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="W2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="X2" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:24">
       <x:c r="A3" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>50.6</x:v>
@@ -1068,10 +1071,10 @@
         <x:v>5.8</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I3" s="0">
         <x:v>9</x:v>
@@ -1080,19 +1083,19 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M3" s="0">
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="P3" s="0">
         <x:v>15000000</x:v>
@@ -1104,36 +1107,36 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="T3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="X3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:24">
       <x:c r="A4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>44.6</x:v>
@@ -1145,7 +1148,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I4" s="0">
         <x:v>9</x:v>
@@ -1154,7 +1157,7 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>28</x:v>
@@ -1163,10 +1166,10 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P4" s="0">
         <x:v>14000000</x:v>
@@ -1178,36 +1181,36 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="S4" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="T4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U4" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="X4" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:24">
       <x:c r="A5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>44.3</x:v>
@@ -1219,7 +1222,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I5" s="0">
         <x:v>9</x:v>
@@ -1228,19 +1231,19 @@
         <x:v>1967</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="M5" s="0">
         <x:v>2.55</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="P5" s="0">
         <x:v>13300000</x:v>
@@ -1252,36 +1255,36 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="T5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="X5" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:24">
       <x:c r="A6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>38.7</x:v>
@@ -1290,10 +1293,10 @@
         <x:v>10.1</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I6" s="0">
         <x:v>12</x:v>
@@ -1302,7 +1305,7 @@
         <x:v>1986</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>28</x:v>
@@ -1311,10 +1314,10 @@
         <x:v>2.65</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="P6" s="0">
         <x:v>12990000</x:v>
@@ -1326,36 +1329,36 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="X6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:24">
       <x:c r="A7" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>36.8</x:v>
@@ -1364,10 +1367,10 @@
         <x:v>7.8</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>15</x:v>
@@ -1376,7 +1379,7 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>28</x:v>
@@ -1385,10 +1388,10 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="P7" s="0">
         <x:v>13000000</x:v>
@@ -1397,25 +1400,25 @@
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="T7" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="X7" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1450,10 +1453,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>23</x:v>
@@ -1461,121 +1464,121 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="0">
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D3" s="0">
         <x:v>14000000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D4" s="0">
         <x:v>13300000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>13200000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="0">
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D8" s="0">
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
@@ -1592,7 +1595,7 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1624,12 +1627,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:21">
       <x:c r="A1" s="3" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:21" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
@@ -1641,22 +1644,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
         <x:v>7</x:v>
@@ -1674,30 +1677,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P2" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="S2" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="T2" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="U2" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:21">
       <x:c r="A3" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>28</x:v>
@@ -1715,7 +1718,7 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I3" s="4">
         <x:v>46119</x:v>
@@ -1750,10 +1753,10 @@
     </x:row>
     <x:row r="4" spans="1:21">
       <x:c r="A4" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>28</x:v>
@@ -1771,7 +1774,7 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>73</x:v>
@@ -1797,10 +1800,10 @@
     </x:row>
     <x:row r="5" spans="1:21">
       <x:c r="A5" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>28</x:v>
@@ -1818,7 +1821,7 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I5" s="4">
         <x:v>46266</x:v>
@@ -1844,10 +1847,10 @@
     </x:row>
     <x:row r="6" spans="1:21">
       <x:c r="A6" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>28</x:v>
@@ -1865,7 +1868,7 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>28</x:v>
@@ -1888,13 +1891,13 @@
     </x:row>
     <x:row r="7" spans="1:21">
       <x:c r="A7" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>41</x:v>
@@ -1909,10 +1912,10 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>28</x:v>
@@ -1938,10 +1941,10 @@
     </x:row>
     <x:row r="8" spans="1:21">
       <x:c r="A8" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>28</x:v>
@@ -1959,7 +1962,7 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>28</x:v>
@@ -1977,15 +1980,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:21">
       <x:c r="A9" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>28</x:v>
@@ -2003,7 +2006,7 @@
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>24</x:v>
@@ -2024,15 +2027,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:21">
       <x:c r="A10" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>28</x:v>
@@ -2050,7 +2053,7 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
         <x:v>28</x:v>
@@ -2068,18 +2071,18 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S10" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:21">
       <x:c r="A11" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>51.5</x:v>
@@ -2094,7 +2097,7 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>28</x:v>
@@ -2112,15 +2115,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:21">
       <x:c r="A12" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>28</x:v>
@@ -2138,7 +2141,7 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I12" s="4">
         <x:v>46308</x:v>
@@ -2159,15 +2162,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:21">
       <x:c r="A13" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>26</x:v>
@@ -2185,13 +2188,13 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M13" s="0">
         <x:v>1965</x:v>
@@ -2203,10 +2206,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2238,35 +2241,35 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C3" s="4">
         <x:v>46048</x:v>
@@ -2275,7 +2278,7 @@
         <x:v>9990000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>28</x:v>
@@ -2283,10 +2286,10 @@
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C4" s="4">
         <x:v>46119</x:v>
@@ -2295,18 +2298,18 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C5" s="4">
         <x:v>46067</x:v>
@@ -2315,7 +2318,7 @@
         <x:v>11700000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>28</x:v>
@@ -2323,10 +2326,10 @@
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C6" s="4">
         <x:v>46129</x:v>
@@ -2335,7 +2338,7 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>28</x:v>
@@ -2343,38 +2346,38 @@
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
       <x:c r="A9" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C9" s="4">
         <x:v>46076</x:v>
@@ -2383,7 +2386,7 @@
         <x:v>22990000</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>28</x:v>
@@ -2391,10 +2394,10 @@
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C10" s="4">
         <x:v>46118</x:v>
@@ -2403,7 +2406,7 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>28</x:v>
@@ -2411,27 +2414,27 @@
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>23230000</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C12" s="4">
         <x:v>46153</x:v>
@@ -2440,7 +2443,7 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>28</x:v>
@@ -2448,10 +2451,10 @@
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C13" s="4">
         <x:v>46162</x:v>
@@ -2460,7 +2463,7 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>28</x:v>
@@ -2468,10 +2471,10 @@
     </x:row>
     <x:row r="14" spans="1:6">
       <x:c r="A14" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C14" s="4">
         <x:v>46174</x:v>
@@ -2480,7 +2483,7 @@
         <x:v>22000000</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>28</x:v>
@@ -2488,10 +2491,10 @@
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C15" s="4">
         <x:v>46266</x:v>
@@ -2500,46 +2503,46 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C18" s="4">
         <x:v>46107</x:v>
@@ -2548,7 +2551,7 @@
         <x:v>17400000</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>28</x:v>
@@ -2556,10 +2559,10 @@
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C19" s="4">
         <x:v>46132</x:v>
@@ -2568,7 +2571,7 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>28</x:v>
@@ -2576,24 +2579,24 @@
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C21" s="4">
         <x:v>46112</x:v>
@@ -2602,7 +2605,7 @@
         <x:v>23900000</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>28</x:v>
@@ -2610,27 +2613,27 @@
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>23500000</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C23" s="4">
         <x:v>46193</x:v>
@@ -2639,7 +2642,7 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>28</x:v>
@@ -2647,24 +2650,24 @@
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C25" s="4">
         <x:v>46138</x:v>
@@ -2673,7 +2676,7 @@
         <x:v>10990000</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>28</x:v>
@@ -2681,10 +2684,10 @@
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C26" s="4">
         <x:v>46168</x:v>
@@ -2693,7 +2696,7 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>28</x:v>
@@ -2701,24 +2704,24 @@
     </x:row>
     <x:row r="27" spans="1:6">
       <x:c r="A27" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C28" s="4">
         <x:v>46142</x:v>
@@ -2727,7 +2730,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>28</x:v>
@@ -2735,41 +2738,41 @@
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C31" s="4">
         <x:v>46179</x:v>
@@ -2778,7 +2781,7 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>28</x:v>
@@ -2786,52 +2789,52 @@
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C35" s="4">
         <x:v>46184</x:v>
@@ -2840,7 +2843,7 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>28</x:v>
@@ -2848,24 +2851,24 @@
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C37" s="4">
         <x:v>46187</x:v>
@@ -2874,7 +2877,7 @@
         <x:v>29000000</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>28</x:v>
@@ -2882,10 +2885,10 @@
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C38" s="4">
         <x:v>46206</x:v>
@@ -2894,7 +2897,7 @@
         <x:v>28500000</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>28</x:v>
@@ -2902,10 +2905,10 @@
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C39" s="4">
         <x:v>46308</x:v>
@@ -2914,18 +2917,18 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C40" s="4">
         <x:v>46220</x:v>
@@ -2934,7 +2937,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>28</x:v>
@@ -2942,16 +2945,16 @@
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -1116,7 +1116,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
         <x:v>49</x:v>
@@ -1190,7 +1190,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
         <x:v>58</x:v>
@@ -1264,7 +1264,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
         <x:v>67</x:v>
@@ -1338,7 +1338,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
         <x:v>77</x:v>
@@ -1412,7 +1412,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
         <x:v>90</x:v>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -129,10 +129,10 @@
     <x:t>2026-10-18T15:15:29.2091171+00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-20T15:24:02.1835444+00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-19T21:30:06.0000000+03:00</x:t>
+    <x:t>2026-10-24T15:17:14.3474247+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-22T21:30:59.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
@@ -171,7 +171,7 @@
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-19T21:30:24.0000000+03:00</x:t>
+    <x:t>2026-10-22T21:30:55.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
@@ -198,7 +198,7 @@
     <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-19T21:30:16.0000000+03:00</x:t>
+    <x:t>2026-10-23T11:51:25.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
@@ -225,7 +225,7 @@
     <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-19T21:30:20.0000000+03:00</x:t>
+    <x:t>2026-10-22T16:50:33.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
@@ -255,7 +255,7 @@
     <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-19T21:30:11.0000000+03:00</x:t>
+    <x:t>2026-10-22T21:31:03.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
@@ -997,7 +997,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>49.6</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>15.8</x:v>
@@ -1116,7 +1116,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
         <x:v>49</x:v>
@@ -1190,7 +1190,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
         <x:v>58</x:v>
@@ -1264,7 +1264,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
         <x:v>67</x:v>
@@ -1338,7 +1338,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
         <x:v>77</x:v>
@@ -1412,7 +1412,7 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
         <x:v>90</x:v>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -13,7 +13,7 @@
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Объявления!$A$1:$X$7</x:definedName>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$9</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'История цен'!$A$1:$E$10</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Старый архив'!$A$2:$U$13</x:definedName>
     <x:definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Цены старого архива'!$A$2:$F$41</x:definedName>
   </x:definedNames>
@@ -129,132 +129,138 @@
     <x:t>2026-10-18T15:15:29.2091171+00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-26T15:56:29.4269095+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-26T17:27:49.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334110300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 балкон</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Панельный</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Центральное</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Гражданский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T15:24:18Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-25T16:03:30.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334909733</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Академическая</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-25T16:03:38.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>330348790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Проспект Славы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-25T16:03:26.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332861239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 из 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Комендантский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Нет в профиле</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-24T15:17:14.3474247+00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-22T21:30:59.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334110300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 балкон</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Панельный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Центральное</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Гражданский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T15:24:18Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-22T21:30:55.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334909733</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Академическая</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-23T11:51:25.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>330348790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Проспект Славы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-22T16:50:33.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>332861239</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10 из 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Комендантский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-10-22T21:31:03.0000000+03:00</x:t>
   </x:si>
   <x:si>
@@ -283,9 +289,6 @@
   </x:si>
   <x:si>
     <x:t>7 мин на транспорте</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Нет в профиле</x:t>
   </x:si>
   <x:si>
     <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
@@ -1030,7 +1033,7 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="Q2" s="0">
-        <x:v>28000000</x:v>
+        <x:v>27800000</x:v>
       </x:c>
       <x:c r="R2" s="0" t="s">
         <x:v>33</x:v>
@@ -1116,7 +1119,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
         <x:v>49</x:v>
@@ -1190,7 +1193,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
         <x:v>58</x:v>
@@ -1264,7 +1267,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
         <x:v>67</x:v>
@@ -1326,39 +1329,39 @@
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="R6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S6" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="T6" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="U6" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="X6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:24">
       <x:c r="A7" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>36.8</x:v>
@@ -1367,10 +1370,10 @@
         <x:v>7.8</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I7" s="0">
         <x:v>15</x:v>
@@ -1379,7 +1382,7 @@
         <x:v>1970</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>28</x:v>
@@ -1388,10 +1391,10 @@
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="P7" s="0">
         <x:v>13000000</x:v>
@@ -1400,25 +1403,25 @@
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="R7" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S7" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="T7" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="U7" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="X7" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1436,7 +1439,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E9"/>
+  <x:dimension ref="A1:E10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="19.710625" style="0" customWidth="1"/>
@@ -1453,10 +1456,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>23</x:v>
@@ -1521,7 +1524,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D5" s="0">
         <x:v>13200000</x:v>
@@ -1544,7 +1547,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
@@ -1555,21 +1558,21 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D7" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>48</x:v>
@@ -1578,7 +1581,7 @@
         <x:v>13000000</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
@@ -1598,8 +1601,25 @@
         <x:v>37</x:v>
       </x:c>
     </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D10" s="0">
+        <x:v>27800000</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:E9"/>
+  <x:autoFilter ref="A1:E10"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -1627,12 +1647,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:21">
       <x:c r="A1" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:21" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
@@ -1644,22 +1664,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
         <x:v>7</x:v>
@@ -1677,30 +1697,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P2" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="S2" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="T2" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="U2" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:21">
       <x:c r="A3" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>28</x:v>
@@ -1718,7 +1738,7 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I3" s="4">
         <x:v>46119</x:v>
@@ -1753,10 +1773,10 @@
     </x:row>
     <x:row r="4" spans="1:21">
       <x:c r="A4" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>28</x:v>
@@ -1774,7 +1794,7 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>73</x:v>
@@ -1800,10 +1820,10 @@
     </x:row>
     <x:row r="5" spans="1:21">
       <x:c r="A5" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>28</x:v>
@@ -1821,7 +1841,7 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I5" s="4">
         <x:v>46266</x:v>
@@ -1847,10 +1867,10 @@
     </x:row>
     <x:row r="6" spans="1:21">
       <x:c r="A6" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>28</x:v>
@@ -1868,7 +1888,7 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>28</x:v>
@@ -1891,10 +1911,10 @@
     </x:row>
     <x:row r="7" spans="1:21">
       <x:c r="A7" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>71</x:v>
@@ -1912,10 +1932,10 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>28</x:v>
@@ -1941,10 +1961,10 @@
     </x:row>
     <x:row r="8" spans="1:21">
       <x:c r="A8" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>28</x:v>
@@ -1962,7 +1982,7 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>28</x:v>
@@ -1980,15 +2000,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:21">
       <x:c r="A9" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>28</x:v>
@@ -2006,7 +2026,7 @@
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>24</x:v>
@@ -2027,15 +2047,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:21">
       <x:c r="A10" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>28</x:v>
@@ -2053,7 +2073,7 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
         <x:v>28</x:v>
@@ -2076,13 +2096,13 @@
     </x:row>
     <x:row r="11" spans="1:21">
       <x:c r="A11" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>51.5</x:v>
@@ -2097,7 +2117,7 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>28</x:v>
@@ -2115,15 +2135,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:21">
       <x:c r="A12" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>28</x:v>
@@ -2141,7 +2161,7 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I12" s="4">
         <x:v>46308</x:v>
@@ -2162,15 +2182,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S12" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:21">
       <x:c r="A13" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>26</x:v>
@@ -2188,10 +2208,10 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
         <x:v>43</x:v>
@@ -2206,10 +2226,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2241,35 +2261,35 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C3" s="4">
         <x:v>46048</x:v>
@@ -2278,7 +2298,7 @@
         <x:v>9990000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>28</x:v>
@@ -2286,10 +2306,10 @@
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C4" s="4">
         <x:v>46119</x:v>
@@ -2298,18 +2318,18 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C5" s="4">
         <x:v>46067</x:v>
@@ -2318,7 +2338,7 @@
         <x:v>11700000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>28</x:v>
@@ -2326,10 +2346,10 @@
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C6" s="4">
         <x:v>46129</x:v>
@@ -2338,7 +2358,7 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>28</x:v>
@@ -2346,38 +2366,38 @@
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
       <x:c r="A9" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C9" s="4">
         <x:v>46076</x:v>
@@ -2386,7 +2406,7 @@
         <x:v>22990000</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>28</x:v>
@@ -2394,10 +2414,10 @@
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C10" s="4">
         <x:v>46118</x:v>
@@ -2406,7 +2426,7 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>28</x:v>
@@ -2414,27 +2434,27 @@
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>23230000</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C12" s="4">
         <x:v>46153</x:v>
@@ -2443,7 +2463,7 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>28</x:v>
@@ -2451,10 +2471,10 @@
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C13" s="4">
         <x:v>46162</x:v>
@@ -2463,7 +2483,7 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>28</x:v>
@@ -2471,10 +2491,10 @@
     </x:row>
     <x:row r="14" spans="1:6">
       <x:c r="A14" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C14" s="4">
         <x:v>46174</x:v>
@@ -2483,7 +2503,7 @@
         <x:v>22000000</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>28</x:v>
@@ -2491,10 +2511,10 @@
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C15" s="4">
         <x:v>46266</x:v>
@@ -2503,46 +2523,46 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C18" s="4">
         <x:v>46107</x:v>
@@ -2551,7 +2571,7 @@
         <x:v>17400000</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>28</x:v>
@@ -2559,10 +2579,10 @@
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C19" s="4">
         <x:v>46132</x:v>
@@ -2571,7 +2591,7 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>28</x:v>
@@ -2579,24 +2599,24 @@
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C21" s="4">
         <x:v>46112</x:v>
@@ -2605,7 +2625,7 @@
         <x:v>23900000</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>28</x:v>
@@ -2613,27 +2633,27 @@
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>23500000</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C23" s="4">
         <x:v>46193</x:v>
@@ -2642,7 +2662,7 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>28</x:v>
@@ -2650,24 +2670,24 @@
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C25" s="4">
         <x:v>46138</x:v>
@@ -2676,7 +2696,7 @@
         <x:v>10990000</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>28</x:v>
@@ -2684,10 +2704,10 @@
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C26" s="4">
         <x:v>46168</x:v>
@@ -2696,7 +2716,7 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>28</x:v>
@@ -2704,24 +2724,24 @@
     </x:row>
     <x:row r="27" spans="1:6">
       <x:c r="A27" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C28" s="4">
         <x:v>46142</x:v>
@@ -2730,7 +2750,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>28</x:v>
@@ -2738,41 +2758,41 @@
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C31" s="4">
         <x:v>46179</x:v>
@@ -2781,7 +2801,7 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>28</x:v>
@@ -2789,52 +2809,52 @@
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C35" s="4">
         <x:v>46184</x:v>
@@ -2843,7 +2863,7 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>28</x:v>
@@ -2851,24 +2871,24 @@
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C37" s="4">
         <x:v>46187</x:v>
@@ -2877,7 +2897,7 @@
         <x:v>29000000</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>28</x:v>
@@ -2885,10 +2905,10 @@
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C38" s="4">
         <x:v>46206</x:v>
@@ -2897,7 +2917,7 @@
         <x:v>28500000</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>28</x:v>
@@ -2905,10 +2925,10 @@
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C39" s="4">
         <x:v>46308</x:v>
@@ -2917,18 +2937,18 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C40" s="4">
         <x:v>46220</x:v>
@@ -2937,7 +2957,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>28</x:v>
@@ -2945,16 +2965,16 @@
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -129,187 +129,190 @@
     <x:t>2026-10-18T15:15:29.2091171+00:00</x:t>
   </x:si>
   <x:si>
+    <x:t>2026-10-28T15:40:00.3255780+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-27T21:36:51.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334110300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 балкон</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Панельный</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Центральное</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Гражданский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T15:24:18Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-27T21:36:46.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334909733</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Академическая</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-27T21:36:56.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>330348790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8 из 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Проспект Славы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-27T21:36:41.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>332861239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10 из 12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Комендантский проспект</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13 мин пешком</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Нет в профиле</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-24T15:17:14.3474247+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-22T21:31:03.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>334653328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1 лоджия</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9 из 15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Кирпичный</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Парк Победы</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7 мин на транспорте</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-16T15:20:38.3153475+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-12T09:46:40.0000000+03:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.cian.ru/sale/flat/334653328/</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Дата наблюдения</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Цена, ₽</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-14T17:11:29.7796317+00:00</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-10-26T15:56:29.4269095+00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-26T17:27:49.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334110300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Прометей, м. Гражданский проспект, Учительская улица, 19К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 балкон</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Панельный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Центральное</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Гражданский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-09-21T09:12:08.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T15:24:18Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-25T16:03:30.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334909733</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Калининский, Академическое, м. Академическая, Гражданский проспект, 83К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Академическая</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-25T16:03:38.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>330348790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2-комн. квартира, Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Фрунзенский, № 72, м. Проспект Славы, Бухарестская улица, 86К1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8 из 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Проспект Славы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-25T16:03:26.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>332861239</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Приморский, Озеро Долгое, м. Комендантский проспект, улица Маршала Новикова, 9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10 из 12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Комендантский проспект</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13 мин пешком</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Нет в профиле</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-12T11:55:30.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-24T15:17:14.3474247+00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-22T21:31:03.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/332861239/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>334653328</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1-комн. квартира, Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Санкт-Петербург, р-н Московский, Гагаринское, м. Московская, проспект Космонавтов, 22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1 лоджия</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9 из 15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Кирпичный</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Парк Победы</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7 мин на транспорте</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-07T08:38:25.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-16T15:20:38.3153475+00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-12T09:46:40.0000000+03:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.cian.ru/sale/flat/334653328/</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Дата наблюдения</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Цена, ₽</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-14T17:11:29.7796317+00:00</x:t>
   </x:si>
   <x:si>
     <x:t>СТАРЫЕ И НЕТОЧНЫЕ ДАННЫЕ — сведения о продаже со слов пользователя, не сверены с Цианом. Дата исчезновения не равна дате сделки.</x:t>
@@ -1119,7 +1122,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
         <x:v>49</x:v>
@@ -1193,7 +1196,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
         <x:v>58</x:v>
@@ -1267,7 +1270,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
         <x:v>67</x:v>
@@ -1341,7 +1344,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
         <x:v>79</x:v>
@@ -1415,7 +1418,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
         <x:v>91</x:v>
@@ -1609,7 +1612,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D10" s="0">
         <x:v>27800000</x:v>
@@ -1647,12 +1650,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:21">
       <x:c r="A1" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:21" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
@@ -1664,22 +1667,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
         <x:v>7</x:v>
@@ -1697,30 +1700,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="P2" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="S2" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="T2" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="U2" s="2" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:21">
       <x:c r="A3" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>28</x:v>
@@ -1738,7 +1741,7 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I3" s="4">
         <x:v>46119</x:v>
@@ -1773,10 +1776,10 @@
     </x:row>
     <x:row r="4" spans="1:21">
       <x:c r="A4" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>28</x:v>
@@ -1794,7 +1797,7 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J4" s="0">
         <x:v>73</x:v>
@@ -1820,10 +1823,10 @@
     </x:row>
     <x:row r="5" spans="1:21">
       <x:c r="A5" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>28</x:v>
@@ -1841,7 +1844,7 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I5" s="4">
         <x:v>46266</x:v>
@@ -1867,10 +1870,10 @@
     </x:row>
     <x:row r="6" spans="1:21">
       <x:c r="A6" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>28</x:v>
@@ -1888,7 +1891,7 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
         <x:v>28</x:v>
@@ -1911,10 +1914,10 @@
     </x:row>
     <x:row r="7" spans="1:21">
       <x:c r="A7" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>71</x:v>
@@ -1932,10 +1935,10 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>28</x:v>
@@ -1961,10 +1964,10 @@
     </x:row>
     <x:row r="8" spans="1:21">
       <x:c r="A8" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>28</x:v>
@@ -1982,7 +1985,7 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
         <x:v>28</x:v>
@@ -2000,15 +2003,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S8" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:21">
       <x:c r="A9" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>28</x:v>
@@ -2026,7 +2029,7 @@
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="J9" s="0">
         <x:v>24</x:v>
@@ -2047,15 +2050,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:21">
       <x:c r="A10" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>28</x:v>
@@ -2073,7 +2076,7 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
         <x:v>28</x:v>
@@ -2096,13 +2099,13 @@
     </x:row>
     <x:row r="11" spans="1:21">
       <x:c r="A11" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>51.5</x:v>
@@ -2117,7 +2120,7 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
         <x:v>28</x:v>
@@ -2135,15 +2138,15 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="S11" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:21">
       <x:c r="A12" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>28</x:v>
@@ -2161,7 +2164,7 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I12" s="4">
         <x:v>46308</x:v>
@@ -2187,10 +2190,10 @@
     </x:row>
     <x:row r="13" spans="1:21">
       <x:c r="A13" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>26</x:v>
@@ -2208,10 +2211,10 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
         <x:v>43</x:v>
@@ -2226,10 +2229,10 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="R13" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="S13" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2261,35 +2264,35 @@
   <x:sheetData>
     <x:row r="1" spans="1:6">
       <x:c r="A1" s="3" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:6" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D2" s="2" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
       <x:c r="A3" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C3" s="4">
         <x:v>46048</x:v>
@@ -2298,7 +2301,7 @@
         <x:v>9990000</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>28</x:v>
@@ -2306,10 +2309,10 @@
     </x:row>
     <x:row r="4" spans="1:6">
       <x:c r="A4" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C4" s="4">
         <x:v>46119</x:v>
@@ -2318,18 +2321,18 @@
         <x:v>9600000</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
       <x:c r="A5" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="4">
         <x:v>46067</x:v>
@@ -2338,7 +2341,7 @@
         <x:v>11700000</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>28</x:v>
@@ -2346,10 +2349,10 @@
     </x:row>
     <x:row r="6" spans="1:6">
       <x:c r="A6" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C6" s="4">
         <x:v>46129</x:v>
@@ -2358,7 +2361,7 @@
         <x:v>11500000</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>28</x:v>
@@ -2366,38 +2369,38 @@
     </x:row>
     <x:row r="7" spans="1:6">
       <x:c r="A7" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
       <x:c r="A8" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
       <x:c r="A9" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C9" s="4">
         <x:v>46076</x:v>
@@ -2406,7 +2409,7 @@
         <x:v>22990000</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>28</x:v>
@@ -2414,10 +2417,10 @@
     </x:row>
     <x:row r="10" spans="1:6">
       <x:c r="A10" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C10" s="4">
         <x:v>46118</x:v>
@@ -2426,7 +2429,7 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>28</x:v>
@@ -2434,27 +2437,27 @@
     </x:row>
     <x:row r="11" spans="1:6">
       <x:c r="A11" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D11" s="0">
         <x:v>23230000</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
       <x:c r="A12" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C12" s="4">
         <x:v>46153</x:v>
@@ -2463,7 +2466,7 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
         <x:v>28</x:v>
@@ -2471,10 +2474,10 @@
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C13" s="4">
         <x:v>46162</x:v>
@@ -2483,7 +2486,7 @@
         <x:v>22500000</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>28</x:v>
@@ -2491,10 +2494,10 @@
     </x:row>
     <x:row r="14" spans="1:6">
       <x:c r="A14" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C14" s="4">
         <x:v>46174</x:v>
@@ -2503,7 +2506,7 @@
         <x:v>22000000</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>28</x:v>
@@ -2511,10 +2514,10 @@
     </x:row>
     <x:row r="15" spans="1:6">
       <x:c r="A15" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C15" s="4">
         <x:v>46266</x:v>
@@ -2523,46 +2526,46 @@
         <x:v>21000000</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
       <x:c r="A16" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
       <x:c r="A17" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
       <x:c r="A18" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C18" s="4">
         <x:v>46107</x:v>
@@ -2571,7 +2574,7 @@
         <x:v>17400000</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
         <x:v>28</x:v>
@@ -2579,10 +2582,10 @@
     </x:row>
     <x:row r="19" spans="1:6">
       <x:c r="A19" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C19" s="4">
         <x:v>46132</x:v>
@@ -2591,7 +2594,7 @@
         <x:v>16990000</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
         <x:v>28</x:v>
@@ -2599,24 +2602,24 @@
     </x:row>
     <x:row r="20" spans="1:6">
       <x:c r="A20" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
       <x:c r="A21" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C21" s="4">
         <x:v>46112</x:v>
@@ -2625,7 +2628,7 @@
         <x:v>23900000</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
         <x:v>28</x:v>
@@ -2633,27 +2636,27 @@
     </x:row>
     <x:row r="22" spans="1:6">
       <x:c r="A22" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D22" s="0">
         <x:v>23500000</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:6">
       <x:c r="A23" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C23" s="4">
         <x:v>46193</x:v>
@@ -2662,7 +2665,7 @@
         <x:v>23000000</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
         <x:v>28</x:v>
@@ -2670,24 +2673,24 @@
     </x:row>
     <x:row r="24" spans="1:6">
       <x:c r="A24" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
       <x:c r="A25" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C25" s="4">
         <x:v>46138</x:v>
@@ -2696,7 +2699,7 @@
         <x:v>10990000</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
         <x:v>28</x:v>
@@ -2704,10 +2707,10 @@
     </x:row>
     <x:row r="26" spans="1:6">
       <x:c r="A26" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C26" s="4">
         <x:v>46168</x:v>
@@ -2716,7 +2719,7 @@
         <x:v>10800000</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
         <x:v>28</x:v>
@@ -2724,24 +2727,24 @@
     </x:row>
     <x:row r="27" spans="1:6">
       <x:c r="A27" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:6">
       <x:c r="A28" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C28" s="4">
         <x:v>46142</x:v>
@@ -2750,7 +2753,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
         <x:v>28</x:v>
@@ -2758,41 +2761,41 @@
     </x:row>
     <x:row r="29" spans="1:6">
       <x:c r="A29" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D29" s="0">
         <x:v>12800000</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
       <x:c r="A30" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
       <x:c r="A31" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C31" s="4">
         <x:v>46179</x:v>
@@ -2801,7 +2804,7 @@
         <x:v>10500000</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
         <x:v>28</x:v>
@@ -2809,52 +2812,52 @@
     </x:row>
     <x:row r="32" spans="1:6">
       <x:c r="A32" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:6">
       <x:c r="A33" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:6">
       <x:c r="A34" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:6">
       <x:c r="A35" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C35" s="4">
         <x:v>46184</x:v>
@@ -2863,7 +2866,7 @@
         <x:v>15000000</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
         <x:v>28</x:v>
@@ -2871,24 +2874,24 @@
     </x:row>
     <x:row r="36" spans="1:6">
       <x:c r="A36" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:6">
       <x:c r="A37" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C37" s="4">
         <x:v>46187</x:v>
@@ -2897,7 +2900,7 @@
         <x:v>29000000</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
         <x:v>28</x:v>
@@ -2905,10 +2908,10 @@
     </x:row>
     <x:row r="38" spans="1:6">
       <x:c r="A38" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C38" s="4">
         <x:v>46206</x:v>
@@ -2917,7 +2920,7 @@
         <x:v>28500000</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
         <x:v>28</x:v>
@@ -2925,10 +2928,10 @@
     </x:row>
     <x:row r="39" spans="1:6">
       <x:c r="A39" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C39" s="4">
         <x:v>46308</x:v>
@@ -2937,18 +2940,18 @@
         <x:v>28000000</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
       <x:c r="A40" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C40" s="4">
         <x:v>46220</x:v>
@@ -2957,7 +2960,7 @@
         <x:v>12990000</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
         <x:v>28</x:v>
@@ -2965,16 +2968,16 @@
     </x:row>
     <x:row r="41" spans="1:6">
       <x:c r="A41" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cian-monitor/cian-monitor.xlsx
+++ b/cian-monitor/cian-monitor.xlsx
@@ -129,10 +129,10 @@
     <x:t>2026-10-18T15:15:29.2091171+00:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-28T15:40:00.3255780+00:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-27T21:36:51.0000000+03:00</x:t>
+    <x:t>2026-10-30T15:39:42.3745314+00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-29T10:46:41.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/335053290/</x:t>
@@ -171,7 +171,7 @@
     <x:t>2026-10-14T15:24:18Z</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-27T21:36:46.0000000+03:00</x:t>
+    <x:t>2026-10-29T10:46:35.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334110300/</x:t>
@@ -198,7 +198,7 @@
     <x:t>2026-10-13T19:40:19.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-27T21:36:56.0000000+03:00</x:t>
+    <x:t>2026-10-29T10:46:46.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/334909733/</x:t>
@@ -225,7 +225,7 @@
     <x:t>2026-05-24T11:43:17.0000000+03:00</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-27T21:36:41.0000000+03:00</x:t>
+    <x:t>2026-10-29T10:46:30.0000000+03:00</x:t>
   </x:si>
   <x:si>
     <x:t>https://www.cian.ru/sale/flat/330348790/</x:t>
@@ -1122,7 +1122,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V3" s="0">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
         <x:v>49</x:v>
@@ -1196,7 +1196,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V4" s="0">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="W4" s="0" t="s">
         <x:v>58</x:v>
@@ -1270,7 +1270,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="V5" s="0">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
         <x:v>67</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="V6" s="0">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="W6" s="0" t="s">
         <x:v>79</x:v>
@@ -1418,7 +1418,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="V7" s="0">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="W7" s="0" t="s">
         <x:v>91</x:v>
